--- a/AI_ML_Daily_Tracker.xlsx
+++ b/AI_ML_Daily_Tracker.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="774">
   <si>
     <t>🤖  AI / ML ENGINEER – 12-MONTH STREAK TRACKER</t>
   </si>
@@ -2727,8 +2727,8 @@
     <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;\ * #,##0_ ;_ &quot;₹&quot;\ * \-#,##0_ ;_ &quot;₹&quot;\ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="0.0"/>
-    <numFmt numFmtId="181" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="181" formatCode="0.0"/>
     <numFmt numFmtId="182" formatCode="0.0\%"/>
   </numFmts>
   <fonts count="70">
@@ -2829,6 +2829,18 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF9CA3AF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF4F46E5"/>
       <name val="Arial"/>
@@ -2863,18 +2875,6 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF22C55E"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF9CA3AF"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -3032,6 +3032,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FF0D9488"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF4B5563"/>
       <name val="Arial"/>
@@ -3048,13 +3055,6 @@
       <i/>
       <sz val="10"/>
       <color rgb="FF065F46"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
-      <color rgb="FF0D9488"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -3990,36 +3990,36 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4027,16 +4027,16 @@
     <xf numFmtId="0" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4045,16 +4045,16 @@
     <xf numFmtId="0" fontId="26" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4063,16 +4063,16 @@
     <xf numFmtId="0" fontId="28" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4081,16 +4081,16 @@
     <xf numFmtId="0" fontId="30" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4099,16 +4099,16 @@
     <xf numFmtId="0" fontId="32" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4117,16 +4117,16 @@
     <xf numFmtId="0" fontId="34" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4135,16 +4135,16 @@
     <xf numFmtId="0" fontId="36" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4175,6 +4175,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="44" fillId="21" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -4187,131 +4190,128 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="6" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="7" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="8" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="9" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="10" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="11" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="26" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="47" fillId="21" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="12" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4326,7 +4326,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -4903,7 +4903,7 @@
       <c r="K3" s="85"/>
       <c r="L3" s="85"/>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="2:11">
+    <row r="5" ht="18" customHeight="1" spans="2:12">
       <c r="B5" s="86" t="s">
         <v>2</v>
       </c>
@@ -4925,304 +4925,304 @@
       </c>
       <c r="K5" s="71"/>
     </row>
-    <row r="6" ht="49.5" customHeight="1" spans="2:11">
+    <row r="6" ht="49.5" customHeight="1" spans="2:12">
       <c r="B6" s="89">
         <f>'📅 Tracker'!P2</f>
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="C6" s="89"/>
       <c r="D6" s="90">
         <f>'📅 Tracker'!P3</f>
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="E6" s="90"/>
       <c r="F6" s="91">
         <f>'📅 Tracker'!P4</f>
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="G6" s="91"/>
       <c r="H6" s="92">
         <f>'📅 Tracker'!P5</f>
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="I6" s="92"/>
-      <c r="J6" s="130">
+      <c r="J6" s="93">
         <f>'📅 Tracker'!P6</f>
-        <v>4.16666666666667</v>
-      </c>
-      <c r="K6" s="130"/>
-    </row>
-    <row r="7" ht="21.75" customHeight="1" spans="2:11">
-      <c r="B7" s="93"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-    </row>
-    <row r="9" ht="19.5" customHeight="1" spans="2:11">
-      <c r="B9" s="94" t="s">
+        <v>14.8809523809524</v>
+      </c>
+      <c r="K6" s="93"/>
+    </row>
+    <row r="7" ht="21.75" customHeight="1" spans="2:12">
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+    </row>
+    <row r="9" ht="19.5" customHeight="1" spans="2:12">
+      <c r="B9" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="95" t="s">
+      <c r="C9" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95" t="s">
+      <c r="D9" s="96"/>
+      <c r="E9" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="95"/>
-      <c r="G9" s="94" t="s">
+      <c r="F9" s="96"/>
+      <c r="G9" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="94" t="s">
+      <c r="H9" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="95" t="s">
+      <c r="I9" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="95"/>
-      <c r="K9" s="95"/>
-    </row>
-    <row r="10" ht="21.75" customHeight="1" spans="2:11">
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+    </row>
+    <row r="10" ht="21.75" customHeight="1" spans="2:12">
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="96" t="s">
+      <c r="C10" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="96"/>
-      <c r="E10" s="97" t="s">
+      <c r="D10" s="97"/>
+      <c r="E10" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="97"/>
-      <c r="G10" s="98">
+      <c r="F10" s="98"/>
+      <c r="G10" s="99">
         <v>56</v>
       </c>
-      <c r="H10" s="99">
+      <c r="H10" s="100">
         <f>COUNTIFS('📅 Tracker'!G:G,"Phase 1",'📅 Tracker'!H:H,"✓")</f>
-        <v>14</v>
-      </c>
-      <c r="I10" s="131">
+        <v>49</v>
+      </c>
+      <c r="I10" s="101">
         <f>IFERROR(H10/56,0)</f>
-        <v>0.25</v>
-      </c>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-    </row>
-    <row r="11" ht="21.75" customHeight="1" spans="2:11">
+        <v>0.875</v>
+      </c>
+      <c r="J10" s="101"/>
+      <c r="K10" s="101"/>
+    </row>
+    <row r="11" ht="21.75" customHeight="1" spans="2:12">
       <c r="B11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="100" t="s">
+      <c r="C11" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="100"/>
-      <c r="E11" s="101" t="s">
+      <c r="D11" s="102"/>
+      <c r="E11" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="101"/>
-      <c r="G11" s="102">
+      <c r="F11" s="103"/>
+      <c r="G11" s="104">
         <v>28</v>
       </c>
-      <c r="H11" s="103">
+      <c r="H11" s="105">
         <f>COUNTIFS('📅 Tracker'!G:G,"Phase 2",'📅 Tracker'!H:H,"✓")</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="132">
+        <v>1</v>
+      </c>
+      <c r="I11" s="106">
         <f>IFERROR(H11/28,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="132"/>
-      <c r="K11" s="132"/>
-    </row>
-    <row r="12" ht="21.75" customHeight="1" spans="2:11">
+        <v>0.0357142857142857</v>
+      </c>
+      <c r="J11" s="106"/>
+      <c r="K11" s="106"/>
+    </row>
+    <row r="12" ht="21.75" customHeight="1" spans="2:12">
       <c r="B12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="104" t="s">
+      <c r="C12" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="104"/>
-      <c r="E12" s="105" t="s">
+      <c r="D12" s="107"/>
+      <c r="E12" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="105"/>
-      <c r="G12" s="106">
+      <c r="F12" s="108"/>
+      <c r="G12" s="109">
         <v>28</v>
       </c>
-      <c r="H12" s="107">
+      <c r="H12" s="110">
         <f>COUNTIFS('📅 Tracker'!G:G,"Phase 3",'📅 Tracker'!H:H,"✓")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="133">
+      <c r="I12" s="111">
         <f>IFERROR(H12/28,0)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="133"/>
-      <c r="K12" s="133"/>
-    </row>
-    <row r="13" ht="21.75" customHeight="1" spans="2:11">
+      <c r="J12" s="111"/>
+      <c r="K12" s="111"/>
+    </row>
+    <row r="13" ht="21.75" customHeight="1" spans="2:12">
       <c r="B13" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="108" t="s">
+      <c r="C13" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="108"/>
-      <c r="E13" s="109" t="s">
+      <c r="D13" s="112"/>
+      <c r="E13" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="109"/>
-      <c r="G13" s="110">
+      <c r="F13" s="113"/>
+      <c r="G13" s="114">
         <v>56</v>
       </c>
-      <c r="H13" s="111">
+      <c r="H13" s="115">
         <f>COUNTIFS('📅 Tracker'!G:G,"Phase 4",'📅 Tracker'!H:H,"✓")</f>
         <v>0</v>
       </c>
-      <c r="I13" s="134">
+      <c r="I13" s="116">
         <f>IFERROR(H13/56,0)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="134"/>
-      <c r="K13" s="134"/>
-    </row>
-    <row r="14" ht="21.75" customHeight="1" spans="2:11">
+      <c r="J13" s="116"/>
+      <c r="K13" s="116"/>
+    </row>
+    <row r="14" ht="21.75" customHeight="1" spans="2:12">
       <c r="B14" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="112" t="s">
+      <c r="C14" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="112"/>
-      <c r="E14" s="113" t="s">
+      <c r="D14" s="117"/>
+      <c r="E14" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="113"/>
-      <c r="G14" s="114">
+      <c r="F14" s="118"/>
+      <c r="G14" s="119">
         <v>56</v>
       </c>
-      <c r="H14" s="115">
+      <c r="H14" s="120">
         <f>COUNTIFS('📅 Tracker'!G:G,"Phase 5",'📅 Tracker'!H:H,"✓")</f>
         <v>0</v>
       </c>
-      <c r="I14" s="135">
+      <c r="I14" s="121">
         <f>IFERROR(H14/56,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="135"/>
-      <c r="K14" s="135"/>
-    </row>
-    <row r="15" ht="21.75" customHeight="1" spans="2:11">
+      <c r="J14" s="121"/>
+      <c r="K14" s="121"/>
+    </row>
+    <row r="15" ht="21.75" customHeight="1" spans="2:12">
       <c r="B15" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="116" t="s">
+      <c r="C15" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="116"/>
-      <c r="E15" s="117" t="s">
+      <c r="D15" s="122"/>
+      <c r="E15" s="123" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="117"/>
-      <c r="G15" s="118">
+      <c r="F15" s="123"/>
+      <c r="G15" s="124">
         <v>56</v>
       </c>
-      <c r="H15" s="119">
+      <c r="H15" s="125">
         <f>COUNTIFS('📅 Tracker'!G:G,"Phase 6",'📅 Tracker'!H:H,"✓")</f>
         <v>0</v>
       </c>
-      <c r="I15" s="136">
+      <c r="I15" s="126">
         <f>IFERROR(H15/56,0)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="136"/>
-      <c r="K15" s="136"/>
-    </row>
-    <row r="16" ht="21.75" customHeight="1" spans="2:11">
+      <c r="J15" s="126"/>
+      <c r="K15" s="126"/>
+    </row>
+    <row r="16" ht="21.75" customHeight="1" spans="2:12">
       <c r="B16" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="120" t="s">
+      <c r="C16" s="127" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="120"/>
-      <c r="E16" s="121" t="s">
+      <c r="D16" s="127"/>
+      <c r="E16" s="128" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="121"/>
-      <c r="G16" s="122">
+      <c r="F16" s="128"/>
+      <c r="G16" s="129">
         <v>28</v>
       </c>
-      <c r="H16" s="123">
+      <c r="H16" s="130">
         <f>COUNTIFS('📅 Tracker'!G:G,"Phase 7",'📅 Tracker'!H:H,"✓")</f>
         <v>0</v>
       </c>
-      <c r="I16" s="137">
+      <c r="I16" s="131">
         <f>IFERROR(H16/28,0)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="137"/>
-      <c r="K16" s="137"/>
+      <c r="J16" s="131"/>
+      <c r="K16" s="131"/>
     </row>
     <row r="17" ht="21.75" customHeight="1" spans="2:11">
       <c r="B17" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="124" t="s">
+      <c r="C17" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="124"/>
-      <c r="E17" s="125" t="s">
+      <c r="D17" s="132"/>
+      <c r="E17" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="125"/>
-      <c r="G17" s="126">
+      <c r="F17" s="133"/>
+      <c r="G17" s="134">
         <v>28</v>
       </c>
-      <c r="H17" s="127">
+      <c r="H17" s="135">
         <f>COUNTIFS('📅 Tracker'!G:G,"Phase 8",'📅 Tracker'!H:H,"✓")</f>
         <v>0</v>
       </c>
-      <c r="I17" s="138">
+      <c r="I17" s="136">
         <f>IFERROR(H17/28,0)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="138"/>
-      <c r="K17" s="138"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
     </row>
     <row r="20" ht="27.75" customHeight="1" spans="2:11">
-      <c r="B20" s="128" t="s">
+      <c r="B20" s="137" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="128"/>
-      <c r="D20" s="128"/>
-      <c r="E20" s="128"/>
-      <c r="F20" s="128"/>
-      <c r="G20" s="128"/>
-      <c r="H20" s="128"/>
-      <c r="I20" s="128"/>
-      <c r="J20" s="128"/>
-      <c r="K20" s="128"/>
+      <c r="C20" s="137"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="137"/>
+      <c r="G20" s="137"/>
+      <c r="H20" s="137"/>
+      <c r="I20" s="137"/>
+      <c r="J20" s="137"/>
+      <c r="K20" s="137"/>
     </row>
     <row r="21" ht="27.75" customHeight="1" spans="2:11">
-      <c r="B21" s="129" t="s">
+      <c r="B21" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="129"/>
-      <c r="D21" s="129"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="129"/>
-      <c r="H21" s="129"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="129"/>
-      <c r="K21" s="129"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="138"/>
+      <c r="F21" s="138"/>
+      <c r="G21" s="138"/>
+      <c r="H21" s="138"/>
+      <c r="I21" s="138"/>
+      <c r="J21" s="138"/>
+      <c r="K21" s="138"/>
     </row>
   </sheetData>
   <mergeCells count="46">
@@ -5301,7 +5301,7 @@
     <col min="18" max="18" width="11.1111111111111"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52" customHeight="1" spans="2:16">
+    <row r="1" ht="52" customHeight="1" spans="2:19">
       <c r="B1" s="25" t="s">
         <v>39</v>
       </c>
@@ -5313,82 +5313,82 @@
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
       <c r="J1" s="25"/>
-      <c r="P1" s="34" t="s">
+      <c r="P1" s="26" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" ht="26.4" spans="2:16">
-      <c r="B2" s="26" t="s">
+    <row r="2" ht="26.4" spans="2:19">
+      <c r="B2" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="I2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="J2" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="O2" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="P2" s="36">
+      <c r="P2" s="29">
         <f>COUNTIF(H3:H402,"✓")</f>
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1" spans="2:19">
-      <c r="B3" s="27">
+      <c r="B3" s="30">
         <v>1</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="31" t="s">
         <v>48</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="36" t="s">
         <v>50</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="O3" s="35" t="s">
+      <c r="O3" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="P3" s="36">
+      <c r="P3" s="29">
         <f>336-P2</f>
-        <v>322</v>
-      </c>
-      <c r="R3" s="39">
+        <v>286</v>
+      </c>
+      <c r="R3" s="37">
         <v>46074</v>
       </c>
       <c r="S3" t="s">
@@ -5396,385 +5396,385 @@
       </c>
     </row>
     <row r="4" ht="41" customHeight="1" spans="2:19">
-      <c r="B4" s="27">
+      <c r="B4" s="30">
         <v>2</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="31" t="s">
         <v>54</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="I4" s="36" t="s">
         <v>55</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="35" t="s">
+      <c r="O4" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="29">
         <f>IFERROR(MATCH(FALSE(),EXACT(H3:H338,"✓"),0)-1,COUNTIF(H3:H338,"✓"))</f>
-        <v>14</v>
-      </c>
-      <c r="R4" s="39">
+        <v>50</v>
+      </c>
+      <c r="R4" s="37">
         <v>46410</v>
       </c>
       <c r="S4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" ht="37.5" customHeight="1" spans="2:16">
-      <c r="B5" s="27">
+    <row r="5" ht="37.5" customHeight="1" spans="2:19">
+      <c r="B5" s="30">
         <v>3</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="31" t="s">
         <v>58</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="36" t="s">
         <v>59</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="O5" s="35" t="s">
+      <c r="O5" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="P5" s="36">
+      <c r="P5" s="29">
         <f>P2</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="37.5" customHeight="1" spans="2:16">
-      <c r="B6" s="27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" ht="37.5" customHeight="1" spans="2:19">
+      <c r="B6" s="30">
         <v>4</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="31" t="s">
         <v>61</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="I6" s="36" t="s">
         <v>62</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="O6" s="35" t="s">
+      <c r="O6" s="28" t="s">
         <v>63</v>
       </c>
       <c r="P6" s="38">
         <f>IFERROR(P2/336*100,0)</f>
-        <v>4.16666666666667</v>
-      </c>
-    </row>
-    <row r="7" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B7" s="27">
+        <v>14.8809523809524</v>
+      </c>
+    </row>
+    <row r="7" ht="37.5" customHeight="1" spans="2:19">
+      <c r="B7" s="30">
         <v>5</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="31" t="s">
         <v>64</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="H7" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="37" t="s">
+      <c r="I7" s="36" t="s">
         <v>65</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B8" s="27">
+    <row r="8" ht="37.5" customHeight="1" spans="2:19">
+      <c r="B8" s="30">
         <v>6</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="31" t="s">
         <v>66</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="37" t="s">
+      <c r="I8" s="36" t="s">
         <v>67</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B9" s="27">
+    <row r="9" ht="37.5" customHeight="1" spans="2:19">
+      <c r="B9" s="30">
         <v>7</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="31" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="36" t="s">
         <v>69</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-    </row>
-    <row r="11" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B11" s="27">
+    <row r="10" ht="7.5" customHeight="1" spans="2:19">
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+    </row>
+    <row r="11" ht="37.5" customHeight="1" spans="2:19">
+      <c r="B11" s="30">
         <v>8</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="31" t="s">
         <v>70</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="H11" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="36" t="s">
         <v>71</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="12" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B12" s="27">
+    <row r="12" ht="37.5" customHeight="1" spans="2:19">
+      <c r="B12" s="30">
         <v>9</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="31" t="s">
         <v>72</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I12" s="37" t="s">
+      <c r="I12" s="36" t="s">
         <v>73</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B13" s="27">
+    <row r="13" ht="37.5" customHeight="1" spans="2:19">
+      <c r="B13" s="30">
         <v>10</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="31" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="30" t="s">
+      <c r="F13" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="H13" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I13" s="37" t="s">
+      <c r="I13" s="36" t="s">
         <v>75</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B14" s="27">
+    <row r="14" ht="37.5" customHeight="1" spans="2:19">
+      <c r="B14" s="30">
         <v>11</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="31" t="s">
         <v>76</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="30" t="s">
+      <c r="F14" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I14" s="37" t="s">
+      <c r="I14" s="36" t="s">
         <v>77</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B15" s="27">
+    <row r="15" ht="37.5" customHeight="1" spans="2:19">
+      <c r="B15" s="30">
         <v>12</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="31" t="s">
         <v>78</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="30" t="s">
+      <c r="F15" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="H15" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="37" t="s">
+      <c r="I15" s="36" t="s">
         <v>79</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="16" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B16" s="27">
+    <row r="16" ht="37.5" customHeight="1" spans="2:19">
+      <c r="B16" s="30">
         <v>13</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="31" t="s">
         <v>80</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="30" t="s">
+      <c r="F16" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="37" t="s">
+      <c r="I16" s="36" t="s">
         <v>81</v>
       </c>
       <c r="J16" s="6" t="s">
@@ -5782,28 +5782,28 @@
       </c>
     </row>
     <row r="17" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B17" s="27">
+      <c r="B17" s="30">
         <v>14</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="31" t="s">
         <v>82</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="30" t="s">
+      <c r="F17" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="I17" s="37" t="s">
+      <c r="I17" s="36" t="s">
         <v>83</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -5811,37 +5811,39 @@
       </c>
     </row>
     <row r="18" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
     </row>
     <row r="19" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B19" s="27">
+      <c r="B19" s="30">
         <v>15</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="31" t="s">
         <v>84</v>
       </c>
       <c r="D19" s="3">
         <v>1</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="30" t="s">
+      <c r="F19" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="32"/>
-      <c r="I19" s="37" t="s">
+      <c r="H19" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" s="36" t="s">
         <v>85</v>
       </c>
       <c r="J19" s="6" t="s">
@@ -5849,26 +5851,28 @@
       </c>
     </row>
     <row r="20" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B20" s="27">
+      <c r="B20" s="30">
         <v>16</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="31" t="s">
         <v>86</v>
       </c>
       <c r="D20" s="3">
         <v>1</v>
       </c>
-      <c r="E20" s="29" t="s">
+      <c r="E20" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="30" t="s">
+      <c r="F20" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H20" s="32"/>
-      <c r="I20" s="37" t="s">
+      <c r="H20" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="36" t="s">
         <v>87</v>
       </c>
       <c r="J20" s="6" t="s">
@@ -5876,26 +5880,28 @@
       </c>
     </row>
     <row r="21" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B21" s="27">
+      <c r="B21" s="30">
         <v>17</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="31" t="s">
         <v>88</v>
       </c>
       <c r="D21" s="3">
         <v>1</v>
       </c>
-      <c r="E21" s="29" t="s">
+      <c r="E21" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="30" t="s">
+      <c r="F21" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="32"/>
-      <c r="I21" s="37" t="s">
+      <c r="H21" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" s="36" t="s">
         <v>89</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -5903,26 +5909,28 @@
       </c>
     </row>
     <row r="22" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B22" s="27">
+      <c r="B22" s="30">
         <v>18</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="31" t="s">
         <v>90</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
       </c>
-      <c r="E22" s="29" t="s">
+      <c r="E22" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="30" t="s">
+      <c r="F22" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G22" s="31" t="s">
+      <c r="G22" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="32"/>
-      <c r="I22" s="37" t="s">
+      <c r="H22" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="36" t="s">
         <v>91</v>
       </c>
       <c r="J22" s="6" t="s">
@@ -5930,26 +5938,28 @@
       </c>
     </row>
     <row r="23" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B23" s="27">
+      <c r="B23" s="30">
         <v>19</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="31" t="s">
         <v>92</v>
       </c>
       <c r="D23" s="3">
         <v>1</v>
       </c>
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="30" t="s">
+      <c r="F23" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G23" s="31" t="s">
+      <c r="G23" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="32"/>
-      <c r="I23" s="37" t="s">
+      <c r="H23" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" s="36" t="s">
         <v>93</v>
       </c>
       <c r="J23" s="6" t="s">
@@ -5957,26 +5967,28 @@
       </c>
     </row>
     <row r="24" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B24" s="27">
+      <c r="B24" s="30">
         <v>20</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="31" t="s">
         <v>94</v>
       </c>
       <c r="D24" s="3">
         <v>1</v>
       </c>
-      <c r="E24" s="29" t="s">
+      <c r="E24" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F24" s="30" t="s">
+      <c r="F24" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H24" s="32"/>
-      <c r="I24" s="37" t="s">
+      <c r="H24" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" s="36" t="s">
         <v>95</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -5984,26 +5996,28 @@
       </c>
     </row>
     <row r="25" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B25" s="27">
+      <c r="B25" s="30">
         <v>21</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="31" t="s">
         <v>96</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H25" s="32"/>
-      <c r="I25" s="37" t="s">
+      <c r="H25" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="36" t="s">
         <v>97</v>
       </c>
       <c r="J25" s="6" t="s">
@@ -6011,37 +6025,39 @@
       </c>
     </row>
     <row r="26" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
     </row>
     <row r="27" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B27" s="27">
+      <c r="B27" s="30">
         <v>22</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="31" t="s">
         <v>98</v>
       </c>
       <c r="D27" s="3">
         <v>1</v>
       </c>
-      <c r="E27" s="29" t="s">
+      <c r="E27" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F27" s="30" t="s">
+      <c r="F27" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H27" s="32"/>
-      <c r="I27" s="37" t="s">
+      <c r="H27" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I27" s="36" t="s">
         <v>99</v>
       </c>
       <c r="J27" s="6" t="s">
@@ -6049,26 +6065,28 @@
       </c>
     </row>
     <row r="28" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B28" s="27">
+      <c r="B28" s="30">
         <v>23</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="31" t="s">
         <v>100</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="30" t="s">
+      <c r="F28" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H28" s="32"/>
-      <c r="I28" s="37" t="s">
+      <c r="H28" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" s="36" t="s">
         <v>101</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -6076,26 +6094,28 @@
       </c>
     </row>
     <row r="29" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B29" s="27">
+      <c r="B29" s="30">
         <v>24</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="31" t="s">
         <v>102</v>
       </c>
       <c r="D29" s="3">
         <v>1</v>
       </c>
-      <c r="E29" s="29" t="s">
+      <c r="E29" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="30" t="s">
+      <c r="F29" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G29" s="31" t="s">
+      <c r="G29" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="32"/>
-      <c r="I29" s="37" t="s">
+      <c r="H29" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I29" s="36" t="s">
         <v>103</v>
       </c>
       <c r="J29" s="6" t="s">
@@ -6103,26 +6123,28 @@
       </c>
     </row>
     <row r="30" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B30" s="27">
+      <c r="B30" s="30">
         <v>25</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="31" t="s">
         <v>104</v>
       </c>
       <c r="D30" s="3">
         <v>1</v>
       </c>
-      <c r="E30" s="29" t="s">
+      <c r="E30" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="30" t="s">
+      <c r="F30" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G30" s="31" t="s">
+      <c r="G30" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H30" s="32"/>
-      <c r="I30" s="37" t="s">
+      <c r="H30" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I30" s="36" t="s">
         <v>105</v>
       </c>
       <c r="J30" s="6" t="s">
@@ -6130,26 +6152,28 @@
       </c>
     </row>
     <row r="31" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B31" s="27">
+      <c r="B31" s="30">
         <v>26</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="31" t="s">
         <v>106</v>
       </c>
       <c r="D31" s="3">
         <v>1</v>
       </c>
-      <c r="E31" s="29" t="s">
+      <c r="E31" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="30" t="s">
+      <c r="F31" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H31" s="32"/>
-      <c r="I31" s="37" t="s">
+      <c r="H31" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I31" s="36" t="s">
         <v>107</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -6157,26 +6181,28 @@
       </c>
     </row>
     <row r="32" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B32" s="27">
+      <c r="B32" s="30">
         <v>27</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="31" t="s">
         <v>108</v>
       </c>
       <c r="D32" s="3">
         <v>1</v>
       </c>
-      <c r="E32" s="29" t="s">
+      <c r="E32" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="30" t="s">
+      <c r="F32" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G32" s="31" t="s">
+      <c r="G32" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="32"/>
-      <c r="I32" s="37" t="s">
+      <c r="H32" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I32" s="36" t="s">
         <v>109</v>
       </c>
       <c r="J32" s="6" t="s">
@@ -6184,26 +6210,28 @@
       </c>
     </row>
     <row r="33" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B33" s="27">
+      <c r="B33" s="30">
         <v>28</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="31" t="s">
         <v>110</v>
       </c>
       <c r="D33" s="3">
         <v>1</v>
       </c>
-      <c r="E33" s="29" t="s">
+      <c r="E33" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F33" s="30" t="s">
+      <c r="F33" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G33" s="31" t="s">
+      <c r="G33" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H33" s="32"/>
-      <c r="I33" s="37" t="s">
+      <c r="H33" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I33" s="36" t="s">
         <v>111</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -6211,37 +6239,39 @@
       </c>
     </row>
     <row r="34" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
     </row>
     <row r="35" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B35" s="27">
+      <c r="B35" s="30">
         <v>29</v>
       </c>
-      <c r="C35" s="28" t="s">
+      <c r="C35" s="31" t="s">
         <v>112</v>
       </c>
       <c r="D35" s="3">
         <v>1</v>
       </c>
-      <c r="E35" s="29" t="s">
+      <c r="E35" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="30" t="s">
+      <c r="F35" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G35" s="31" t="s">
+      <c r="G35" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="32"/>
-      <c r="I35" s="37" t="s">
+      <c r="H35" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I35" s="36" t="s">
         <v>113</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -6249,26 +6279,28 @@
       </c>
     </row>
     <row r="36" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B36" s="27">
+      <c r="B36" s="30">
         <v>30</v>
       </c>
-      <c r="C36" s="28" t="s">
+      <c r="C36" s="31" t="s">
         <v>114</v>
       </c>
       <c r="D36" s="3">
         <v>1</v>
       </c>
-      <c r="E36" s="29" t="s">
+      <c r="E36" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="30" t="s">
+      <c r="F36" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G36" s="31" t="s">
+      <c r="G36" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H36" s="32"/>
-      <c r="I36" s="37" t="s">
+      <c r="H36" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I36" s="36" t="s">
         <v>115</v>
       </c>
       <c r="J36" s="6" t="s">
@@ -6276,26 +6308,28 @@
       </c>
     </row>
     <row r="37" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B37" s="27">
+      <c r="B37" s="30">
         <v>31</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="C37" s="31" t="s">
         <v>116</v>
       </c>
       <c r="D37" s="3">
         <v>1</v>
       </c>
-      <c r="E37" s="29" t="s">
+      <c r="E37" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F37" s="30" t="s">
+      <c r="F37" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G37" s="31" t="s">
+      <c r="G37" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H37" s="32"/>
-      <c r="I37" s="37" t="s">
+      <c r="H37" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I37" s="36" t="s">
         <v>117</v>
       </c>
       <c r="J37" s="6" t="s">
@@ -6303,26 +6337,28 @@
       </c>
     </row>
     <row r="38" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B38" s="27">
+      <c r="B38" s="30">
         <v>32</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="31" t="s">
         <v>118</v>
       </c>
       <c r="D38" s="3">
         <v>1</v>
       </c>
-      <c r="E38" s="29" t="s">
+      <c r="E38" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F38" s="30" t="s">
+      <c r="F38" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G38" s="31" t="s">
+      <c r="G38" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H38" s="32"/>
-      <c r="I38" s="37" t="s">
+      <c r="H38" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I38" s="36" t="s">
         <v>119</v>
       </c>
       <c r="J38" s="6" t="s">
@@ -6330,26 +6366,28 @@
       </c>
     </row>
     <row r="39" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B39" s="27">
+      <c r="B39" s="30">
         <v>33</v>
       </c>
-      <c r="C39" s="28" t="s">
+      <c r="C39" s="31" t="s">
         <v>120</v>
       </c>
       <c r="D39" s="3">
         <v>1</v>
       </c>
-      <c r="E39" s="29" t="s">
+      <c r="E39" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F39" s="30" t="s">
+      <c r="F39" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G39" s="31" t="s">
+      <c r="G39" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H39" s="32"/>
-      <c r="I39" s="37" t="s">
+      <c r="H39" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I39" s="36" t="s">
         <v>121</v>
       </c>
       <c r="J39" s="6" t="s">
@@ -6357,26 +6395,28 @@
       </c>
     </row>
     <row r="40" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B40" s="27">
+      <c r="B40" s="30">
         <v>34</v>
       </c>
-      <c r="C40" s="28" t="s">
+      <c r="C40" s="31" t="s">
         <v>122</v>
       </c>
       <c r="D40" s="3">
         <v>1</v>
       </c>
-      <c r="E40" s="29" t="s">
+      <c r="E40" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F40" s="30" t="s">
+      <c r="F40" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G40" s="31" t="s">
+      <c r="G40" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H40" s="32"/>
-      <c r="I40" s="37" t="s">
+      <c r="H40" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I40" s="36" t="s">
         <v>123</v>
       </c>
       <c r="J40" s="6" t="s">
@@ -6384,26 +6424,28 @@
       </c>
     </row>
     <row r="41" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B41" s="27">
+      <c r="B41" s="30">
         <v>35</v>
       </c>
-      <c r="C41" s="28" t="s">
+      <c r="C41" s="31" t="s">
         <v>124</v>
       </c>
       <c r="D41" s="3">
         <v>1</v>
       </c>
-      <c r="E41" s="29" t="s">
+      <c r="E41" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F41" s="30" t="s">
+      <c r="F41" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H41" s="32"/>
-      <c r="I41" s="37" t="s">
+      <c r="H41" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I41" s="36" t="s">
         <v>125</v>
       </c>
       <c r="J41" s="6" t="s">
@@ -6411,37 +6453,39 @@
       </c>
     </row>
     <row r="42" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B42" s="33"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
     </row>
     <row r="43" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B43" s="27">
+      <c r="B43" s="30">
         <v>36</v>
       </c>
-      <c r="C43" s="28" t="s">
+      <c r="C43" s="31" t="s">
         <v>126</v>
       </c>
       <c r="D43" s="3">
         <v>1</v>
       </c>
-      <c r="E43" s="29" t="s">
+      <c r="E43" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F43" s="30" t="s">
+      <c r="F43" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G43" s="31" t="s">
+      <c r="G43" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H43" s="32"/>
-      <c r="I43" s="37" t="s">
+      <c r="H43" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I43" s="36" t="s">
         <v>127</v>
       </c>
       <c r="J43" s="6" t="s">
@@ -6449,26 +6493,28 @@
       </c>
     </row>
     <row r="44" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B44" s="27">
+      <c r="B44" s="30">
         <v>37</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="C44" s="31" t="s">
         <v>128</v>
       </c>
       <c r="D44" s="3">
         <v>1</v>
       </c>
-      <c r="E44" s="29" t="s">
+      <c r="E44" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F44" s="30" t="s">
+      <c r="F44" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G44" s="31" t="s">
+      <c r="G44" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H44" s="32"/>
-      <c r="I44" s="37" t="s">
+      <c r="H44" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I44" s="36" t="s">
         <v>129</v>
       </c>
       <c r="J44" s="6" t="s">
@@ -6476,26 +6522,28 @@
       </c>
     </row>
     <row r="45" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B45" s="27">
+      <c r="B45" s="30">
         <v>38</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="31" t="s">
         <v>130</v>
       </c>
       <c r="D45" s="3">
         <v>1</v>
       </c>
-      <c r="E45" s="29" t="s">
+      <c r="E45" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F45" s="30" t="s">
+      <c r="F45" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G45" s="31" t="s">
+      <c r="G45" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H45" s="32"/>
-      <c r="I45" s="37" t="s">
+      <c r="H45" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I45" s="36" t="s">
         <v>131</v>
       </c>
       <c r="J45" s="6" t="s">
@@ -6503,26 +6551,26 @@
       </c>
     </row>
     <row r="46" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B46" s="27">
+      <c r="B46" s="30">
         <v>39</v>
       </c>
-      <c r="C46" s="28" t="s">
+      <c r="C46" s="31" t="s">
         <v>132</v>
       </c>
       <c r="D46" s="3">
         <v>1</v>
       </c>
-      <c r="E46" s="29" t="s">
+      <c r="E46" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F46" s="30" t="s">
+      <c r="F46" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G46" s="31" t="s">
+      <c r="G46" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H46" s="32"/>
-      <c r="I46" s="37" t="s">
+      <c r="H46" s="35"/>
+      <c r="I46" s="36" t="s">
         <v>133</v>
       </c>
       <c r="J46" s="6" t="s">
@@ -6530,26 +6578,26 @@
       </c>
     </row>
     <row r="47" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B47" s="27">
+      <c r="B47" s="30">
         <v>40</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="31" t="s">
         <v>134</v>
       </c>
       <c r="D47" s="3">
         <v>1</v>
       </c>
-      <c r="E47" s="29" t="s">
+      <c r="E47" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F47" s="30" t="s">
+      <c r="F47" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G47" s="31" t="s">
+      <c r="G47" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H47" s="32"/>
-      <c r="I47" s="37" t="s">
+      <c r="H47" s="35"/>
+      <c r="I47" s="36" t="s">
         <v>135</v>
       </c>
       <c r="J47" s="6" t="s">
@@ -6557,26 +6605,26 @@
       </c>
     </row>
     <row r="48" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B48" s="27">
+      <c r="B48" s="30">
         <v>41</v>
       </c>
-      <c r="C48" s="28" t="s">
+      <c r="C48" s="31" t="s">
         <v>136</v>
       </c>
       <c r="D48" s="3">
         <v>1</v>
       </c>
-      <c r="E48" s="29" t="s">
+      <c r="E48" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F48" s="30" t="s">
+      <c r="F48" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G48" s="31" t="s">
+      <c r="G48" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H48" s="32"/>
-      <c r="I48" s="37" t="s">
+      <c r="H48" s="35"/>
+      <c r="I48" s="36" t="s">
         <v>137</v>
       </c>
       <c r="J48" s="6" t="s">
@@ -6584,26 +6632,26 @@
       </c>
     </row>
     <row r="49" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B49" s="27">
+      <c r="B49" s="30">
         <v>42</v>
       </c>
-      <c r="C49" s="28" t="s">
+      <c r="C49" s="31" t="s">
         <v>138</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
       </c>
-      <c r="E49" s="29" t="s">
+      <c r="E49" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F49" s="30" t="s">
+      <c r="F49" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G49" s="31" t="s">
+      <c r="G49" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H49" s="32"/>
-      <c r="I49" s="37" t="s">
+      <c r="H49" s="35"/>
+      <c r="I49" s="36" t="s">
         <v>139</v>
       </c>
       <c r="J49" s="6" t="s">
@@ -6611,37 +6659,39 @@
       </c>
     </row>
     <row r="50" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
-      <c r="H50" s="33"/>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="39"/>
+      <c r="I50" s="39"/>
+      <c r="J50" s="39"/>
     </row>
     <row r="51" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B51" s="27">
+      <c r="B51" s="30">
         <v>43</v>
       </c>
-      <c r="C51" s="28" t="s">
+      <c r="C51" s="31" t="s">
         <v>140</v>
       </c>
       <c r="D51" s="3">
         <v>1</v>
       </c>
-      <c r="E51" s="29" t="s">
+      <c r="E51" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F51" s="30" t="s">
+      <c r="F51" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G51" s="31" t="s">
+      <c r="G51" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H51" s="32"/>
-      <c r="I51" s="37" t="s">
+      <c r="H51" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I51" s="36" t="s">
         <v>141</v>
       </c>
       <c r="J51" s="6" t="s">
@@ -6649,26 +6699,28 @@
       </c>
     </row>
     <row r="52" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B52" s="27">
+      <c r="B52" s="30">
         <v>44</v>
       </c>
-      <c r="C52" s="28" t="s">
+      <c r="C52" s="31" t="s">
         <v>142</v>
       </c>
       <c r="D52" s="3">
         <v>1</v>
       </c>
-      <c r="E52" s="29" t="s">
+      <c r="E52" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F52" s="30" t="s">
+      <c r="F52" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G52" s="31" t="s">
+      <c r="G52" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H52" s="32"/>
-      <c r="I52" s="37" t="s">
+      <c r="H52" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I52" s="36" t="s">
         <v>143</v>
       </c>
       <c r="J52" s="6" t="s">
@@ -6676,26 +6728,28 @@
       </c>
     </row>
     <row r="53" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B53" s="27">
+      <c r="B53" s="30">
         <v>45</v>
       </c>
-      <c r="C53" s="28" t="s">
+      <c r="C53" s="31" t="s">
         <v>144</v>
       </c>
       <c r="D53" s="3">
         <v>1</v>
       </c>
-      <c r="E53" s="29" t="s">
+      <c r="E53" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F53" s="30" t="s">
+      <c r="F53" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G53" s="31" t="s">
+      <c r="G53" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H53" s="32"/>
-      <c r="I53" s="37" t="s">
+      <c r="H53" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I53" s="36" t="s">
         <v>145</v>
       </c>
       <c r="J53" s="6" t="s">
@@ -6703,26 +6757,28 @@
       </c>
     </row>
     <row r="54" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B54" s="27">
+      <c r="B54" s="30">
         <v>46</v>
       </c>
-      <c r="C54" s="28" t="s">
+      <c r="C54" s="31" t="s">
         <v>146</v>
       </c>
       <c r="D54" s="3">
         <v>1</v>
       </c>
-      <c r="E54" s="29" t="s">
+      <c r="E54" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F54" s="30" t="s">
+      <c r="F54" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G54" s="31" t="s">
+      <c r="G54" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H54" s="32"/>
-      <c r="I54" s="37" t="s">
+      <c r="H54" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I54" s="36" t="s">
         <v>147</v>
       </c>
       <c r="J54" s="6" t="s">
@@ -6730,26 +6786,28 @@
       </c>
     </row>
     <row r="55" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B55" s="27">
+      <c r="B55" s="30">
         <v>47</v>
       </c>
-      <c r="C55" s="28" t="s">
+      <c r="C55" s="31" t="s">
         <v>148</v>
       </c>
       <c r="D55" s="3">
         <v>1</v>
       </c>
-      <c r="E55" s="29" t="s">
+      <c r="E55" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F55" s="30" t="s">
+      <c r="F55" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G55" s="31" t="s">
+      <c r="G55" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H55" s="32"/>
-      <c r="I55" s="37" t="s">
+      <c r="H55" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I55" s="36" t="s">
         <v>149</v>
       </c>
       <c r="J55" s="6" t="s">
@@ -6757,26 +6815,26 @@
       </c>
     </row>
     <row r="56" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B56" s="27">
+      <c r="B56" s="30">
         <v>48</v>
       </c>
-      <c r="C56" s="28" t="s">
+      <c r="C56" s="31" t="s">
         <v>150</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
       </c>
-      <c r="E56" s="29" t="s">
+      <c r="E56" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F56" s="30" t="s">
+      <c r="F56" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G56" s="31" t="s">
+      <c r="G56" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H56" s="32"/>
-      <c r="I56" s="37" t="s">
+      <c r="H56" s="35"/>
+      <c r="I56" s="36" t="s">
         <v>151</v>
       </c>
       <c r="J56" s="6" t="s">
@@ -6784,26 +6842,26 @@
       </c>
     </row>
     <row r="57" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B57" s="27">
+      <c r="B57" s="30">
         <v>49</v>
       </c>
-      <c r="C57" s="28" t="s">
+      <c r="C57" s="31" t="s">
         <v>152</v>
       </c>
       <c r="D57" s="3">
         <v>1</v>
       </c>
-      <c r="E57" s="29" t="s">
+      <c r="E57" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F57" s="30" t="s">
+      <c r="F57" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G57" s="31" t="s">
+      <c r="G57" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H57" s="32"/>
-      <c r="I57" s="37" t="s">
+      <c r="H57" s="35"/>
+      <c r="I57" s="36" t="s">
         <v>153</v>
       </c>
       <c r="J57" s="6" t="s">
@@ -6811,37 +6869,39 @@
       </c>
     </row>
     <row r="58" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B58" s="33"/>
-      <c r="C58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
-      <c r="F58" s="33"/>
-      <c r="G58" s="33"/>
-      <c r="H58" s="33"/>
-      <c r="I58" s="33"/>
-      <c r="J58" s="33"/>
+      <c r="B58" s="39"/>
+      <c r="C58" s="39"/>
+      <c r="D58" s="39"/>
+      <c r="E58" s="39"/>
+      <c r="F58" s="39"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="39"/>
+      <c r="I58" s="39"/>
+      <c r="J58" s="39"/>
     </row>
     <row r="59" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B59" s="27">
+      <c r="B59" s="30">
         <v>50</v>
       </c>
-      <c r="C59" s="28" t="s">
+      <c r="C59" s="31" t="s">
         <v>154</v>
       </c>
       <c r="D59" s="3">
         <v>1</v>
       </c>
-      <c r="E59" s="29" t="s">
+      <c r="E59" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="30" t="s">
+      <c r="F59" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G59" s="31" t="s">
+      <c r="G59" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H59" s="32"/>
-      <c r="I59" s="37" t="s">
+      <c r="H59" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I59" s="36" t="s">
         <v>155</v>
       </c>
       <c r="J59" s="6" t="s">
@@ -6849,26 +6909,28 @@
       </c>
     </row>
     <row r="60" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B60" s="27">
+      <c r="B60" s="30">
         <v>51</v>
       </c>
-      <c r="C60" s="28" t="s">
+      <c r="C60" s="31" t="s">
         <v>156</v>
       </c>
       <c r="D60" s="3">
         <v>1</v>
       </c>
-      <c r="E60" s="29" t="s">
+      <c r="E60" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F60" s="30" t="s">
+      <c r="F60" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G60" s="31" t="s">
+      <c r="G60" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H60" s="32"/>
-      <c r="I60" s="37" t="s">
+      <c r="H60" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I60" s="36" t="s">
         <v>157</v>
       </c>
       <c r="J60" s="6" t="s">
@@ -6876,26 +6938,28 @@
       </c>
     </row>
     <row r="61" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B61" s="27">
+      <c r="B61" s="30">
         <v>52</v>
       </c>
-      <c r="C61" s="28" t="s">
+      <c r="C61" s="31" t="s">
         <v>158</v>
       </c>
       <c r="D61" s="3">
         <v>1</v>
       </c>
-      <c r="E61" s="29" t="s">
+      <c r="E61" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F61" s="30" t="s">
+      <c r="F61" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G61" s="31" t="s">
+      <c r="G61" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H61" s="32"/>
-      <c r="I61" s="37" t="s">
+      <c r="H61" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I61" s="36" t="s">
         <v>159</v>
       </c>
       <c r="J61" s="6" t="s">
@@ -6903,26 +6967,28 @@
       </c>
     </row>
     <row r="62" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B62" s="27">
+      <c r="B62" s="30">
         <v>53</v>
       </c>
-      <c r="C62" s="28" t="s">
+      <c r="C62" s="31" t="s">
         <v>160</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
       </c>
-      <c r="E62" s="29" t="s">
+      <c r="E62" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F62" s="30" t="s">
+      <c r="F62" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G62" s="31" t="s">
+      <c r="G62" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H62" s="32"/>
-      <c r="I62" s="37" t="s">
+      <c r="H62" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I62" s="36" t="s">
         <v>161</v>
       </c>
       <c r="J62" s="6" t="s">
@@ -6930,26 +6996,28 @@
       </c>
     </row>
     <row r="63" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B63" s="27">
+      <c r="B63" s="30">
         <v>54</v>
       </c>
-      <c r="C63" s="28" t="s">
+      <c r="C63" s="31" t="s">
         <v>162</v>
       </c>
       <c r="D63" s="3">
         <v>1</v>
       </c>
-      <c r="E63" s="29" t="s">
+      <c r="E63" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F63" s="30" t="s">
+      <c r="F63" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G63" s="31" t="s">
+      <c r="G63" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H63" s="32"/>
-      <c r="I63" s="37" t="s">
+      <c r="H63" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I63" s="36" t="s">
         <v>163</v>
       </c>
       <c r="J63" s="6" t="s">
@@ -6957,26 +7025,28 @@
       </c>
     </row>
     <row r="64" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B64" s="27">
+      <c r="B64" s="30">
         <v>55</v>
       </c>
-      <c r="C64" s="28" t="s">
+      <c r="C64" s="31" t="s">
         <v>164</v>
       </c>
       <c r="D64" s="3">
         <v>1</v>
       </c>
-      <c r="E64" s="29" t="s">
+      <c r="E64" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F64" s="30" t="s">
+      <c r="F64" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G64" s="31" t="s">
+      <c r="G64" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H64" s="32"/>
-      <c r="I64" s="37" t="s">
+      <c r="H64" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I64" s="36" t="s">
         <v>165</v>
       </c>
       <c r="J64" s="6" t="s">
@@ -6984,26 +7054,26 @@
       </c>
     </row>
     <row r="65" ht="37.5" customHeight="1" spans="2:10">
-      <c r="B65" s="27">
+      <c r="B65" s="30">
         <v>56</v>
       </c>
-      <c r="C65" s="28" t="s">
+      <c r="C65" s="31" t="s">
         <v>166</v>
       </c>
       <c r="D65" s="3">
         <v>1</v>
       </c>
-      <c r="E65" s="29" t="s">
+      <c r="E65" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F65" s="30" t="s">
+      <c r="F65" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G65" s="31" t="s">
+      <c r="G65" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H65" s="32"/>
-      <c r="I65" s="37" t="s">
+      <c r="H65" s="35"/>
+      <c r="I65" s="36" t="s">
         <v>167</v>
       </c>
       <c r="J65" s="6" t="s">
@@ -7011,15 +7081,15 @@
       </c>
     </row>
     <row r="66" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B66" s="33"/>
-      <c r="C66" s="33"/>
-      <c r="D66" s="33"/>
-      <c r="E66" s="33"/>
-      <c r="F66" s="33"/>
-      <c r="G66" s="33"/>
-      <c r="H66" s="33"/>
-      <c r="I66" s="33"/>
-      <c r="J66" s="33"/>
+      <c r="B66" s="39"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="39"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="39"/>
+      <c r="I66" s="39"/>
+      <c r="J66" s="39"/>
     </row>
     <row r="67" ht="13.5" customHeight="1" spans="2:10">
       <c r="B67" s="40" t="s">
@@ -7064,8 +7134,10 @@
       <c r="G69" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H69" s="32"/>
-      <c r="I69" s="37" t="s">
+      <c r="H69" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I69" s="36" t="s">
         <v>170</v>
       </c>
       <c r="J69" s="6" t="s">
@@ -7091,8 +7163,8 @@
       <c r="G70" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H70" s="32"/>
-      <c r="I70" s="37" t="s">
+      <c r="H70" s="35"/>
+      <c r="I70" s="36" t="s">
         <v>173</v>
       </c>
       <c r="J70" s="6" t="s">
@@ -7118,8 +7190,8 @@
       <c r="G71" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H71" s="32"/>
-      <c r="I71" s="37" t="s">
+      <c r="H71" s="35"/>
+      <c r="I71" s="36" t="s">
         <v>175</v>
       </c>
       <c r="J71" s="6" t="s">
@@ -7145,8 +7217,8 @@
       <c r="G72" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H72" s="32"/>
-      <c r="I72" s="37" t="s">
+      <c r="H72" s="35"/>
+      <c r="I72" s="36" t="s">
         <v>177</v>
       </c>
       <c r="J72" s="6" t="s">
@@ -7172,8 +7244,8 @@
       <c r="G73" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H73" s="32"/>
-      <c r="I73" s="37" t="s">
+      <c r="H73" s="35"/>
+      <c r="I73" s="36" t="s">
         <v>179</v>
       </c>
       <c r="J73" s="6" t="s">
@@ -7199,8 +7271,8 @@
       <c r="G74" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H74" s="32"/>
-      <c r="I74" s="37" t="s">
+      <c r="H74" s="35"/>
+      <c r="I74" s="36" t="s">
         <v>181</v>
       </c>
       <c r="J74" s="6" t="s">
@@ -7226,8 +7298,8 @@
       <c r="G75" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H75" s="32"/>
-      <c r="I75" s="37" t="s">
+      <c r="H75" s="35"/>
+      <c r="I75" s="36" t="s">
         <v>183</v>
       </c>
       <c r="J75" s="6" t="s">
@@ -7235,15 +7307,15 @@
       </c>
     </row>
     <row r="76" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B76" s="33"/>
-      <c r="C76" s="33"/>
-      <c r="D76" s="33"/>
-      <c r="E76" s="33"/>
-      <c r="F76" s="33"/>
-      <c r="G76" s="33"/>
-      <c r="H76" s="33"/>
-      <c r="I76" s="33"/>
-      <c r="J76" s="33"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
+      <c r="J76" s="39"/>
     </row>
     <row r="77" ht="37.5" customHeight="1" spans="2:10">
       <c r="B77" s="42">
@@ -7264,8 +7336,8 @@
       <c r="G77" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H77" s="32"/>
-      <c r="I77" s="37" t="s">
+      <c r="H77" s="35"/>
+      <c r="I77" s="36" t="s">
         <v>185</v>
       </c>
       <c r="J77" s="6" t="s">
@@ -7291,8 +7363,8 @@
       <c r="G78" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H78" s="32"/>
-      <c r="I78" s="37" t="s">
+      <c r="H78" s="35"/>
+      <c r="I78" s="36" t="s">
         <v>187</v>
       </c>
       <c r="J78" s="6" t="s">
@@ -7318,8 +7390,8 @@
       <c r="G79" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H79" s="32"/>
-      <c r="I79" s="37" t="s">
+      <c r="H79" s="35"/>
+      <c r="I79" s="36" t="s">
         <v>189</v>
       </c>
       <c r="J79" s="6" t="s">
@@ -7345,8 +7417,8 @@
       <c r="G80" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H80" s="32"/>
-      <c r="I80" s="37" t="s">
+      <c r="H80" s="35"/>
+      <c r="I80" s="36" t="s">
         <v>191</v>
       </c>
       <c r="J80" s="6" t="s">
@@ -7372,8 +7444,8 @@
       <c r="G81" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H81" s="32"/>
-      <c r="I81" s="37" t="s">
+      <c r="H81" s="35"/>
+      <c r="I81" s="36" t="s">
         <v>193</v>
       </c>
       <c r="J81" s="6" t="s">
@@ -7399,8 +7471,8 @@
       <c r="G82" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H82" s="32"/>
-      <c r="I82" s="37" t="s">
+      <c r="H82" s="35"/>
+      <c r="I82" s="36" t="s">
         <v>195</v>
       </c>
       <c r="J82" s="6" t="s">
@@ -7426,8 +7498,8 @@
       <c r="G83" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H83" s="32"/>
-      <c r="I83" s="37" t="s">
+      <c r="H83" s="35"/>
+      <c r="I83" s="36" t="s">
         <v>197</v>
       </c>
       <c r="J83" s="6" t="s">
@@ -7435,15 +7507,15 @@
       </c>
     </row>
     <row r="84" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B84" s="33"/>
-      <c r="C84" s="33"/>
-      <c r="D84" s="33"/>
-      <c r="E84" s="33"/>
-      <c r="F84" s="33"/>
-      <c r="G84" s="33"/>
-      <c r="H84" s="33"/>
-      <c r="I84" s="33"/>
-      <c r="J84" s="33"/>
+      <c r="B84" s="39"/>
+      <c r="C84" s="39"/>
+      <c r="D84" s="39"/>
+      <c r="E84" s="39"/>
+      <c r="F84" s="39"/>
+      <c r="G84" s="39"/>
+      <c r="H84" s="39"/>
+      <c r="I84" s="39"/>
+      <c r="J84" s="39"/>
     </row>
     <row r="85" ht="37.5" customHeight="1" spans="2:10">
       <c r="B85" s="42">
@@ -7464,8 +7536,8 @@
       <c r="G85" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H85" s="32"/>
-      <c r="I85" s="37" t="s">
+      <c r="H85" s="35"/>
+      <c r="I85" s="36" t="s">
         <v>199</v>
       </c>
       <c r="J85" s="6" t="s">
@@ -7491,8 +7563,8 @@
       <c r="G86" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H86" s="32"/>
-      <c r="I86" s="37" t="s">
+      <c r="H86" s="35"/>
+      <c r="I86" s="36" t="s">
         <v>201</v>
       </c>
       <c r="J86" s="6" t="s">
@@ -7518,8 +7590,8 @@
       <c r="G87" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H87" s="32"/>
-      <c r="I87" s="37" t="s">
+      <c r="H87" s="35"/>
+      <c r="I87" s="36" t="s">
         <v>203</v>
       </c>
       <c r="J87" s="6" t="s">
@@ -7545,8 +7617,8 @@
       <c r="G88" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H88" s="32"/>
-      <c r="I88" s="37" t="s">
+      <c r="H88" s="35"/>
+      <c r="I88" s="36" t="s">
         <v>205</v>
       </c>
       <c r="J88" s="6" t="s">
@@ -7572,8 +7644,8 @@
       <c r="G89" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H89" s="32"/>
-      <c r="I89" s="37" t="s">
+      <c r="H89" s="35"/>
+      <c r="I89" s="36" t="s">
         <v>207</v>
       </c>
       <c r="J89" s="6" t="s">
@@ -7599,8 +7671,8 @@
       <c r="G90" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H90" s="32"/>
-      <c r="I90" s="37" t="s">
+      <c r="H90" s="35"/>
+      <c r="I90" s="36" t="s">
         <v>209</v>
       </c>
       <c r="J90" s="6" t="s">
@@ -7626,8 +7698,8 @@
       <c r="G91" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H91" s="32"/>
-      <c r="I91" s="37" t="s">
+      <c r="H91" s="35"/>
+      <c r="I91" s="36" t="s">
         <v>211</v>
       </c>
       <c r="J91" s="6" t="s">
@@ -7635,15 +7707,15 @@
       </c>
     </row>
     <row r="92" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B92" s="33"/>
-      <c r="C92" s="33"/>
-      <c r="D92" s="33"/>
-      <c r="E92" s="33"/>
-      <c r="F92" s="33"/>
-      <c r="G92" s="33"/>
-      <c r="H92" s="33"/>
-      <c r="I92" s="33"/>
-      <c r="J92" s="33"/>
+      <c r="B92" s="39"/>
+      <c r="C92" s="39"/>
+      <c r="D92" s="39"/>
+      <c r="E92" s="39"/>
+      <c r="F92" s="39"/>
+      <c r="G92" s="39"/>
+      <c r="H92" s="39"/>
+      <c r="I92" s="39"/>
+      <c r="J92" s="39"/>
     </row>
     <row r="93" ht="37.5" customHeight="1" spans="2:10">
       <c r="B93" s="42">
@@ -7664,8 +7736,8 @@
       <c r="G93" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H93" s="32"/>
-      <c r="I93" s="37" t="s">
+      <c r="H93" s="35"/>
+      <c r="I93" s="36" t="s">
         <v>213</v>
       </c>
       <c r="J93" s="6" t="s">
@@ -7691,8 +7763,8 @@
       <c r="G94" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H94" s="32"/>
-      <c r="I94" s="37" t="s">
+      <c r="H94" s="35"/>
+      <c r="I94" s="36" t="s">
         <v>215</v>
       </c>
       <c r="J94" s="6" t="s">
@@ -7718,8 +7790,8 @@
       <c r="G95" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H95" s="32"/>
-      <c r="I95" s="37" t="s">
+      <c r="H95" s="35"/>
+      <c r="I95" s="36" t="s">
         <v>217</v>
       </c>
       <c r="J95" s="6" t="s">
@@ -7745,8 +7817,8 @@
       <c r="G96" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H96" s="32"/>
-      <c r="I96" s="37" t="s">
+      <c r="H96" s="35"/>
+      <c r="I96" s="36" t="s">
         <v>219</v>
       </c>
       <c r="J96" s="6" t="s">
@@ -7772,8 +7844,8 @@
       <c r="G97" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H97" s="32"/>
-      <c r="I97" s="37" t="s">
+      <c r="H97" s="35"/>
+      <c r="I97" s="36" t="s">
         <v>221</v>
       </c>
       <c r="J97" s="6" t="s">
@@ -7799,8 +7871,8 @@
       <c r="G98" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H98" s="32"/>
-      <c r="I98" s="37" t="s">
+      <c r="H98" s="35"/>
+      <c r="I98" s="36" t="s">
         <v>223</v>
       </c>
       <c r="J98" s="6" t="s">
@@ -7826,8 +7898,8 @@
       <c r="G99" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H99" s="32"/>
-      <c r="I99" s="37" t="s">
+      <c r="H99" s="35"/>
+      <c r="I99" s="36" t="s">
         <v>225</v>
       </c>
       <c r="J99" s="6" t="s">
@@ -7835,15 +7907,15 @@
       </c>
     </row>
     <row r="100" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B100" s="33"/>
-      <c r="C100" s="33"/>
-      <c r="D100" s="33"/>
-      <c r="E100" s="33"/>
-      <c r="F100" s="33"/>
-      <c r="G100" s="33"/>
-      <c r="H100" s="33"/>
-      <c r="I100" s="33"/>
-      <c r="J100" s="33"/>
+      <c r="B100" s="39"/>
+      <c r="C100" s="39"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="39"/>
+      <c r="G100" s="39"/>
+      <c r="H100" s="39"/>
+      <c r="I100" s="39"/>
+      <c r="J100" s="39"/>
     </row>
     <row r="101" ht="13.5" customHeight="1" spans="2:10">
       <c r="B101" s="47" t="s">
@@ -7888,8 +7960,8 @@
       <c r="G103" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H103" s="32"/>
-      <c r="I103" s="37" t="s">
+      <c r="H103" s="35"/>
+      <c r="I103" s="36" t="s">
         <v>228</v>
       </c>
       <c r="J103" s="6" t="s">
@@ -7915,8 +7987,8 @@
       <c r="G104" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H104" s="32"/>
-      <c r="I104" s="37" t="s">
+      <c r="H104" s="35"/>
+      <c r="I104" s="36" t="s">
         <v>231</v>
       </c>
       <c r="J104" s="6" t="s">
@@ -7942,8 +8014,8 @@
       <c r="G105" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H105" s="32"/>
-      <c r="I105" s="37" t="s">
+      <c r="H105" s="35"/>
+      <c r="I105" s="36" t="s">
         <v>233</v>
       </c>
       <c r="J105" s="6" t="s">
@@ -7969,8 +8041,8 @@
       <c r="G106" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H106" s="32"/>
-      <c r="I106" s="37" t="s">
+      <c r="H106" s="35"/>
+      <c r="I106" s="36" t="s">
         <v>235</v>
       </c>
       <c r="J106" s="6" t="s">
@@ -7996,8 +8068,8 @@
       <c r="G107" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H107" s="32"/>
-      <c r="I107" s="37" t="s">
+      <c r="H107" s="35"/>
+      <c r="I107" s="36" t="s">
         <v>237</v>
       </c>
       <c r="J107" s="6" t="s">
@@ -8023,8 +8095,8 @@
       <c r="G108" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H108" s="32"/>
-      <c r="I108" s="37" t="s">
+      <c r="H108" s="35"/>
+      <c r="I108" s="36" t="s">
         <v>239</v>
       </c>
       <c r="J108" s="6" t="s">
@@ -8050,8 +8122,8 @@
       <c r="G109" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H109" s="32"/>
-      <c r="I109" s="37" t="s">
+      <c r="H109" s="35"/>
+      <c r="I109" s="36" t="s">
         <v>241</v>
       </c>
       <c r="J109" s="6" t="s">
@@ -8059,15 +8131,15 @@
       </c>
     </row>
     <row r="110" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B110" s="33"/>
-      <c r="C110" s="33"/>
-      <c r="D110" s="33"/>
-      <c r="E110" s="33"/>
-      <c r="F110" s="33"/>
-      <c r="G110" s="33"/>
-      <c r="H110" s="33"/>
-      <c r="I110" s="33"/>
-      <c r="J110" s="33"/>
+      <c r="B110" s="39"/>
+      <c r="C110" s="39"/>
+      <c r="D110" s="39"/>
+      <c r="E110" s="39"/>
+      <c r="F110" s="39"/>
+      <c r="G110" s="39"/>
+      <c r="H110" s="39"/>
+      <c r="I110" s="39"/>
+      <c r="J110" s="39"/>
     </row>
     <row r="111" ht="37.5" customHeight="1" spans="2:10">
       <c r="B111" s="48">
@@ -8088,8 +8160,8 @@
       <c r="G111" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H111" s="32"/>
-      <c r="I111" s="37" t="s">
+      <c r="H111" s="35"/>
+      <c r="I111" s="36" t="s">
         <v>243</v>
       </c>
       <c r="J111" s="6" t="s">
@@ -8115,8 +8187,8 @@
       <c r="G112" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H112" s="32"/>
-      <c r="I112" s="37" t="s">
+      <c r="H112" s="35"/>
+      <c r="I112" s="36" t="s">
         <v>245</v>
       </c>
       <c r="J112" s="6" t="s">
@@ -8142,8 +8214,8 @@
       <c r="G113" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H113" s="32"/>
-      <c r="I113" s="37" t="s">
+      <c r="H113" s="35"/>
+      <c r="I113" s="36" t="s">
         <v>247</v>
       </c>
       <c r="J113" s="6" t="s">
@@ -8169,8 +8241,8 @@
       <c r="G114" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H114" s="32"/>
-      <c r="I114" s="37" t="s">
+      <c r="H114" s="35"/>
+      <c r="I114" s="36" t="s">
         <v>249</v>
       </c>
       <c r="J114" s="6" t="s">
@@ -8196,8 +8268,8 @@
       <c r="G115" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H115" s="32"/>
-      <c r="I115" s="37" t="s">
+      <c r="H115" s="35"/>
+      <c r="I115" s="36" t="s">
         <v>251</v>
       </c>
       <c r="J115" s="6" t="s">
@@ -8223,8 +8295,8 @@
       <c r="G116" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H116" s="32"/>
-      <c r="I116" s="37" t="s">
+      <c r="H116" s="35"/>
+      <c r="I116" s="36" t="s">
         <v>253</v>
       </c>
       <c r="J116" s="6" t="s">
@@ -8250,8 +8322,8 @@
       <c r="G117" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H117" s="32"/>
-      <c r="I117" s="37" t="s">
+      <c r="H117" s="35"/>
+      <c r="I117" s="36" t="s">
         <v>255</v>
       </c>
       <c r="J117" s="6" t="s">
@@ -8259,15 +8331,15 @@
       </c>
     </row>
     <row r="118" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B118" s="33"/>
-      <c r="C118" s="33"/>
-      <c r="D118" s="33"/>
-      <c r="E118" s="33"/>
-      <c r="F118" s="33"/>
-      <c r="G118" s="33"/>
-      <c r="H118" s="33"/>
-      <c r="I118" s="33"/>
-      <c r="J118" s="33"/>
+      <c r="B118" s="39"/>
+      <c r="C118" s="39"/>
+      <c r="D118" s="39"/>
+      <c r="E118" s="39"/>
+      <c r="F118" s="39"/>
+      <c r="G118" s="39"/>
+      <c r="H118" s="39"/>
+      <c r="I118" s="39"/>
+      <c r="J118" s="39"/>
     </row>
     <row r="119" ht="37.5" customHeight="1" spans="2:10">
       <c r="B119" s="48">
@@ -8288,8 +8360,8 @@
       <c r="G119" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H119" s="32"/>
-      <c r="I119" s="37" t="s">
+      <c r="H119" s="35"/>
+      <c r="I119" s="36" t="s">
         <v>257</v>
       </c>
       <c r="J119" s="6" t="s">
@@ -8315,8 +8387,8 @@
       <c r="G120" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H120" s="32"/>
-      <c r="I120" s="37" t="s">
+      <c r="H120" s="35"/>
+      <c r="I120" s="36" t="s">
         <v>259</v>
       </c>
       <c r="J120" s="6" t="s">
@@ -8342,8 +8414,8 @@
       <c r="G121" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H121" s="32"/>
-      <c r="I121" s="37" t="s">
+      <c r="H121" s="35"/>
+      <c r="I121" s="36" t="s">
         <v>261</v>
       </c>
       <c r="J121" s="6" t="s">
@@ -8369,8 +8441,8 @@
       <c r="G122" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H122" s="32"/>
-      <c r="I122" s="37" t="s">
+      <c r="H122" s="35"/>
+      <c r="I122" s="36" t="s">
         <v>263</v>
       </c>
       <c r="J122" s="6" t="s">
@@ -8396,8 +8468,8 @@
       <c r="G123" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H123" s="32"/>
-      <c r="I123" s="37" t="s">
+      <c r="H123" s="35"/>
+      <c r="I123" s="36" t="s">
         <v>265</v>
       </c>
       <c r="J123" s="6" t="s">
@@ -8423,8 +8495,8 @@
       <c r="G124" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H124" s="32"/>
-      <c r="I124" s="37" t="s">
+      <c r="H124" s="35"/>
+      <c r="I124" s="36" t="s">
         <v>267</v>
       </c>
       <c r="J124" s="6" t="s">
@@ -8450,8 +8522,8 @@
       <c r="G125" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H125" s="32"/>
-      <c r="I125" s="37" t="s">
+      <c r="H125" s="35"/>
+      <c r="I125" s="36" t="s">
         <v>269</v>
       </c>
       <c r="J125" s="6" t="s">
@@ -8459,15 +8531,15 @@
       </c>
     </row>
     <row r="126" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B126" s="33"/>
-      <c r="C126" s="33"/>
-      <c r="D126" s="33"/>
-      <c r="E126" s="33"/>
-      <c r="F126" s="33"/>
-      <c r="G126" s="33"/>
-      <c r="H126" s="33"/>
-      <c r="I126" s="33"/>
-      <c r="J126" s="33"/>
+      <c r="B126" s="39"/>
+      <c r="C126" s="39"/>
+      <c r="D126" s="39"/>
+      <c r="E126" s="39"/>
+      <c r="F126" s="39"/>
+      <c r="G126" s="39"/>
+      <c r="H126" s="39"/>
+      <c r="I126" s="39"/>
+      <c r="J126" s="39"/>
     </row>
     <row r="127" ht="37.5" customHeight="1" spans="2:10">
       <c r="B127" s="48">
@@ -8488,8 +8560,8 @@
       <c r="G127" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H127" s="32"/>
-      <c r="I127" s="37" t="s">
+      <c r="H127" s="35"/>
+      <c r="I127" s="36" t="s">
         <v>271</v>
       </c>
       <c r="J127" s="6" t="s">
@@ -8515,8 +8587,8 @@
       <c r="G128" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H128" s="32"/>
-      <c r="I128" s="37" t="s">
+      <c r="H128" s="35"/>
+      <c r="I128" s="36" t="s">
         <v>273</v>
       </c>
       <c r="J128" s="6" t="s">
@@ -8542,8 +8614,8 @@
       <c r="G129" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H129" s="32"/>
-      <c r="I129" s="37" t="s">
+      <c r="H129" s="35"/>
+      <c r="I129" s="36" t="s">
         <v>275</v>
       </c>
       <c r="J129" s="6" t="s">
@@ -8569,8 +8641,8 @@
       <c r="G130" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H130" s="32"/>
-      <c r="I130" s="37" t="s">
+      <c r="H130" s="35"/>
+      <c r="I130" s="36" t="s">
         <v>277</v>
       </c>
       <c r="J130" s="6" t="s">
@@ -8596,8 +8668,8 @@
       <c r="G131" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H131" s="32"/>
-      <c r="I131" s="37" t="s">
+      <c r="H131" s="35"/>
+      <c r="I131" s="36" t="s">
         <v>279</v>
       </c>
       <c r="J131" s="6" t="s">
@@ -8623,8 +8695,8 @@
       <c r="G132" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H132" s="32"/>
-      <c r="I132" s="37" t="s">
+      <c r="H132" s="35"/>
+      <c r="I132" s="36" t="s">
         <v>281</v>
       </c>
       <c r="J132" s="6" t="s">
@@ -8650,8 +8722,8 @@
       <c r="G133" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H133" s="32"/>
-      <c r="I133" s="37" t="s">
+      <c r="H133" s="35"/>
+      <c r="I133" s="36" t="s">
         <v>283</v>
       </c>
       <c r="J133" s="6" t="s">
@@ -8659,15 +8731,15 @@
       </c>
     </row>
     <row r="134" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B134" s="33"/>
-      <c r="C134" s="33"/>
-      <c r="D134" s="33"/>
-      <c r="E134" s="33"/>
-      <c r="F134" s="33"/>
-      <c r="G134" s="33"/>
-      <c r="H134" s="33"/>
-      <c r="I134" s="33"/>
-      <c r="J134" s="33"/>
+      <c r="B134" s="39"/>
+      <c r="C134" s="39"/>
+      <c r="D134" s="39"/>
+      <c r="E134" s="39"/>
+      <c r="F134" s="39"/>
+      <c r="G134" s="39"/>
+      <c r="H134" s="39"/>
+      <c r="I134" s="39"/>
+      <c r="J134" s="39"/>
     </row>
     <row r="135" ht="13.5" customHeight="1" spans="2:10">
       <c r="B135" s="53" t="s">
@@ -8712,8 +8784,8 @@
       <c r="G137" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H137" s="32"/>
-      <c r="I137" s="37" t="s">
+      <c r="H137" s="35"/>
+      <c r="I137" s="36" t="s">
         <v>286</v>
       </c>
       <c r="J137" s="6" t="s">
@@ -8739,8 +8811,8 @@
       <c r="G138" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H138" s="32"/>
-      <c r="I138" s="37" t="s">
+      <c r="H138" s="35"/>
+      <c r="I138" s="36" t="s">
         <v>289</v>
       </c>
       <c r="J138" s="6" t="s">
@@ -8766,8 +8838,8 @@
       <c r="G139" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H139" s="32"/>
-      <c r="I139" s="37" t="s">
+      <c r="H139" s="35"/>
+      <c r="I139" s="36" t="s">
         <v>291</v>
       </c>
       <c r="J139" s="6" t="s">
@@ -8793,8 +8865,8 @@
       <c r="G140" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H140" s="32"/>
-      <c r="I140" s="37" t="s">
+      <c r="H140" s="35"/>
+      <c r="I140" s="36" t="s">
         <v>293</v>
       </c>
       <c r="J140" s="6" t="s">
@@ -8820,8 +8892,8 @@
       <c r="G141" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H141" s="32"/>
-      <c r="I141" s="37" t="s">
+      <c r="H141" s="35"/>
+      <c r="I141" s="36" t="s">
         <v>295</v>
       </c>
       <c r="J141" s="6" t="s">
@@ -8847,8 +8919,8 @@
       <c r="G142" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H142" s="32"/>
-      <c r="I142" s="37" t="s">
+      <c r="H142" s="35"/>
+      <c r="I142" s="36" t="s">
         <v>297</v>
       </c>
       <c r="J142" s="6" t="s">
@@ -8874,8 +8946,8 @@
       <c r="G143" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H143" s="32"/>
-      <c r="I143" s="37" t="s">
+      <c r="H143" s="35"/>
+      <c r="I143" s="36" t="s">
         <v>299</v>
       </c>
       <c r="J143" s="6" t="s">
@@ -8883,15 +8955,15 @@
       </c>
     </row>
     <row r="144" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B144" s="33"/>
-      <c r="C144" s="33"/>
-      <c r="D144" s="33"/>
-      <c r="E144" s="33"/>
-      <c r="F144" s="33"/>
-      <c r="G144" s="33"/>
-      <c r="H144" s="33"/>
-      <c r="I144" s="33"/>
-      <c r="J144" s="33"/>
+      <c r="B144" s="39"/>
+      <c r="C144" s="39"/>
+      <c r="D144" s="39"/>
+      <c r="E144" s="39"/>
+      <c r="F144" s="39"/>
+      <c r="G144" s="39"/>
+      <c r="H144" s="39"/>
+      <c r="I144" s="39"/>
+      <c r="J144" s="39"/>
     </row>
     <row r="145" ht="37.5" customHeight="1" spans="2:10">
       <c r="B145" s="54">
@@ -8912,8 +8984,8 @@
       <c r="G145" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H145" s="32"/>
-      <c r="I145" s="37" t="s">
+      <c r="H145" s="35"/>
+      <c r="I145" s="36" t="s">
         <v>301</v>
       </c>
       <c r="J145" s="6" t="s">
@@ -8939,8 +9011,8 @@
       <c r="G146" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H146" s="32"/>
-      <c r="I146" s="37" t="s">
+      <c r="H146" s="35"/>
+      <c r="I146" s="36" t="s">
         <v>303</v>
       </c>
       <c r="J146" s="6" t="s">
@@ -8966,8 +9038,8 @@
       <c r="G147" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H147" s="32"/>
-      <c r="I147" s="37" t="s">
+      <c r="H147" s="35"/>
+      <c r="I147" s="36" t="s">
         <v>305</v>
       </c>
       <c r="J147" s="6" t="s">
@@ -8993,8 +9065,8 @@
       <c r="G148" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H148" s="32"/>
-      <c r="I148" s="37" t="s">
+      <c r="H148" s="35"/>
+      <c r="I148" s="36" t="s">
         <v>307</v>
       </c>
       <c r="J148" s="6" t="s">
@@ -9020,8 +9092,8 @@
       <c r="G149" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H149" s="32"/>
-      <c r="I149" s="37" t="s">
+      <c r="H149" s="35"/>
+      <c r="I149" s="36" t="s">
         <v>309</v>
       </c>
       <c r="J149" s="6" t="s">
@@ -9047,8 +9119,8 @@
       <c r="G150" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H150" s="32"/>
-      <c r="I150" s="37" t="s">
+      <c r="H150" s="35"/>
+      <c r="I150" s="36" t="s">
         <v>311</v>
       </c>
       <c r="J150" s="6" t="s">
@@ -9074,8 +9146,8 @@
       <c r="G151" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H151" s="32"/>
-      <c r="I151" s="37" t="s">
+      <c r="H151" s="35"/>
+      <c r="I151" s="36" t="s">
         <v>313</v>
       </c>
       <c r="J151" s="6" t="s">
@@ -9083,15 +9155,15 @@
       </c>
     </row>
     <row r="152" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B152" s="33"/>
-      <c r="C152" s="33"/>
-      <c r="D152" s="33"/>
-      <c r="E152" s="33"/>
-      <c r="F152" s="33"/>
-      <c r="G152" s="33"/>
-      <c r="H152" s="33"/>
-      <c r="I152" s="33"/>
-      <c r="J152" s="33"/>
+      <c r="B152" s="39"/>
+      <c r="C152" s="39"/>
+      <c r="D152" s="39"/>
+      <c r="E152" s="39"/>
+      <c r="F152" s="39"/>
+      <c r="G152" s="39"/>
+      <c r="H152" s="39"/>
+      <c r="I152" s="39"/>
+      <c r="J152" s="39"/>
     </row>
     <row r="153" ht="37.5" customHeight="1" spans="2:10">
       <c r="B153" s="54">
@@ -9112,8 +9184,8 @@
       <c r="G153" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H153" s="32"/>
-      <c r="I153" s="37" t="s">
+      <c r="H153" s="35"/>
+      <c r="I153" s="36" t="s">
         <v>315</v>
       </c>
       <c r="J153" s="6" t="s">
@@ -9139,8 +9211,8 @@
       <c r="G154" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H154" s="32"/>
-      <c r="I154" s="37" t="s">
+      <c r="H154" s="35"/>
+      <c r="I154" s="36" t="s">
         <v>317</v>
       </c>
       <c r="J154" s="6" t="s">
@@ -9166,8 +9238,8 @@
       <c r="G155" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H155" s="32"/>
-      <c r="I155" s="37" t="s">
+      <c r="H155" s="35"/>
+      <c r="I155" s="36" t="s">
         <v>319</v>
       </c>
       <c r="J155" s="6" t="s">
@@ -9193,8 +9265,8 @@
       <c r="G156" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H156" s="32"/>
-      <c r="I156" s="37" t="s">
+      <c r="H156" s="35"/>
+      <c r="I156" s="36" t="s">
         <v>321</v>
       </c>
       <c r="J156" s="6" t="s">
@@ -9220,8 +9292,8 @@
       <c r="G157" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H157" s="32"/>
-      <c r="I157" s="37" t="s">
+      <c r="H157" s="35"/>
+      <c r="I157" s="36" t="s">
         <v>323</v>
       </c>
       <c r="J157" s="6" t="s">
@@ -9247,8 +9319,8 @@
       <c r="G158" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H158" s="32"/>
-      <c r="I158" s="37" t="s">
+      <c r="H158" s="35"/>
+      <c r="I158" s="36" t="s">
         <v>325</v>
       </c>
       <c r="J158" s="6" t="s">
@@ -9274,8 +9346,8 @@
       <c r="G159" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H159" s="32"/>
-      <c r="I159" s="37" t="s">
+      <c r="H159" s="35"/>
+      <c r="I159" s="36" t="s">
         <v>327</v>
       </c>
       <c r="J159" s="6" t="s">
@@ -9283,15 +9355,15 @@
       </c>
     </row>
     <row r="160" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B160" s="33"/>
-      <c r="C160" s="33"/>
-      <c r="D160" s="33"/>
-      <c r="E160" s="33"/>
-      <c r="F160" s="33"/>
-      <c r="G160" s="33"/>
-      <c r="H160" s="33"/>
-      <c r="I160" s="33"/>
-      <c r="J160" s="33"/>
+      <c r="B160" s="39"/>
+      <c r="C160" s="39"/>
+      <c r="D160" s="39"/>
+      <c r="E160" s="39"/>
+      <c r="F160" s="39"/>
+      <c r="G160" s="39"/>
+      <c r="H160" s="39"/>
+      <c r="I160" s="39"/>
+      <c r="J160" s="39"/>
     </row>
     <row r="161" ht="37.5" customHeight="1" spans="2:10">
       <c r="B161" s="54">
@@ -9312,8 +9384,8 @@
       <c r="G161" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H161" s="32"/>
-      <c r="I161" s="37" t="s">
+      <c r="H161" s="35"/>
+      <c r="I161" s="36" t="s">
         <v>329</v>
       </c>
       <c r="J161" s="6" t="s">
@@ -9339,8 +9411,8 @@
       <c r="G162" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H162" s="32"/>
-      <c r="I162" s="37" t="s">
+      <c r="H162" s="35"/>
+      <c r="I162" s="36" t="s">
         <v>331</v>
       </c>
       <c r="J162" s="6" t="s">
@@ -9366,8 +9438,8 @@
       <c r="G163" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H163" s="32"/>
-      <c r="I163" s="37" t="s">
+      <c r="H163" s="35"/>
+      <c r="I163" s="36" t="s">
         <v>333</v>
       </c>
       <c r="J163" s="6" t="s">
@@ -9393,8 +9465,8 @@
       <c r="G164" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H164" s="32"/>
-      <c r="I164" s="37" t="s">
+      <c r="H164" s="35"/>
+      <c r="I164" s="36" t="s">
         <v>335</v>
       </c>
       <c r="J164" s="6" t="s">
@@ -9420,8 +9492,8 @@
       <c r="G165" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H165" s="32"/>
-      <c r="I165" s="37" t="s">
+      <c r="H165" s="35"/>
+      <c r="I165" s="36" t="s">
         <v>337</v>
       </c>
       <c r="J165" s="6" t="s">
@@ -9447,8 +9519,8 @@
       <c r="G166" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H166" s="32"/>
-      <c r="I166" s="37" t="s">
+      <c r="H166" s="35"/>
+      <c r="I166" s="36" t="s">
         <v>339</v>
       </c>
       <c r="J166" s="6" t="s">
@@ -9474,8 +9546,8 @@
       <c r="G167" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H167" s="32"/>
-      <c r="I167" s="37" t="s">
+      <c r="H167" s="35"/>
+      <c r="I167" s="36" t="s">
         <v>341</v>
       </c>
       <c r="J167" s="6" t="s">
@@ -9483,15 +9555,15 @@
       </c>
     </row>
     <row r="168" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B168" s="33"/>
-      <c r="C168" s="33"/>
-      <c r="D168" s="33"/>
-      <c r="E168" s="33"/>
-      <c r="F168" s="33"/>
-      <c r="G168" s="33"/>
-      <c r="H168" s="33"/>
-      <c r="I168" s="33"/>
-      <c r="J168" s="33"/>
+      <c r="B168" s="39"/>
+      <c r="C168" s="39"/>
+      <c r="D168" s="39"/>
+      <c r="E168" s="39"/>
+      <c r="F168" s="39"/>
+      <c r="G168" s="39"/>
+      <c r="H168" s="39"/>
+      <c r="I168" s="39"/>
+      <c r="J168" s="39"/>
     </row>
     <row r="169" ht="37.5" customHeight="1" spans="2:10">
       <c r="B169" s="54">
@@ -9512,8 +9584,8 @@
       <c r="G169" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H169" s="32"/>
-      <c r="I169" s="37" t="s">
+      <c r="H169" s="35"/>
+      <c r="I169" s="36" t="s">
         <v>343</v>
       </c>
       <c r="J169" s="6" t="s">
@@ -9539,8 +9611,8 @@
       <c r="G170" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H170" s="32"/>
-      <c r="I170" s="37" t="s">
+      <c r="H170" s="35"/>
+      <c r="I170" s="36" t="s">
         <v>345</v>
       </c>
       <c r="J170" s="6" t="s">
@@ -9566,8 +9638,8 @@
       <c r="G171" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H171" s="32"/>
-      <c r="I171" s="37" t="s">
+      <c r="H171" s="35"/>
+      <c r="I171" s="36" t="s">
         <v>347</v>
       </c>
       <c r="J171" s="6" t="s">
@@ -9593,8 +9665,8 @@
       <c r="G172" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H172" s="32"/>
-      <c r="I172" s="37" t="s">
+      <c r="H172" s="35"/>
+      <c r="I172" s="36" t="s">
         <v>349</v>
       </c>
       <c r="J172" s="6" t="s">
@@ -9620,8 +9692,8 @@
       <c r="G173" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H173" s="32"/>
-      <c r="I173" s="37" t="s">
+      <c r="H173" s="35"/>
+      <c r="I173" s="36" t="s">
         <v>351</v>
       </c>
       <c r="J173" s="6" t="s">
@@ -9647,8 +9719,8 @@
       <c r="G174" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H174" s="32"/>
-      <c r="I174" s="37" t="s">
+      <c r="H174" s="35"/>
+      <c r="I174" s="36" t="s">
         <v>353</v>
       </c>
       <c r="J174" s="6" t="s">
@@ -9674,8 +9746,8 @@
       <c r="G175" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H175" s="32"/>
-      <c r="I175" s="37" t="s">
+      <c r="H175" s="35"/>
+      <c r="I175" s="36" t="s">
         <v>355</v>
       </c>
       <c r="J175" s="6" t="s">
@@ -9683,15 +9755,15 @@
       </c>
     </row>
     <row r="176" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B176" s="33"/>
-      <c r="C176" s="33"/>
-      <c r="D176" s="33"/>
-      <c r="E176" s="33"/>
-      <c r="F176" s="33"/>
-      <c r="G176" s="33"/>
-      <c r="H176" s="33"/>
-      <c r="I176" s="33"/>
-      <c r="J176" s="33"/>
+      <c r="B176" s="39"/>
+      <c r="C176" s="39"/>
+      <c r="D176" s="39"/>
+      <c r="E176" s="39"/>
+      <c r="F176" s="39"/>
+      <c r="G176" s="39"/>
+      <c r="H176" s="39"/>
+      <c r="I176" s="39"/>
+      <c r="J176" s="39"/>
     </row>
     <row r="177" ht="37.5" customHeight="1" spans="2:10">
       <c r="B177" s="54">
@@ -9712,8 +9784,8 @@
       <c r="G177" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H177" s="32"/>
-      <c r="I177" s="37" t="s">
+      <c r="H177" s="35"/>
+      <c r="I177" s="36" t="s">
         <v>357</v>
       </c>
       <c r="J177" s="6" t="s">
@@ -9739,8 +9811,8 @@
       <c r="G178" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H178" s="32"/>
-      <c r="I178" s="37" t="s">
+      <c r="H178" s="35"/>
+      <c r="I178" s="36" t="s">
         <v>359</v>
       </c>
       <c r="J178" s="6" t="s">
@@ -9766,8 +9838,8 @@
       <c r="G179" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H179" s="32"/>
-      <c r="I179" s="37" t="s">
+      <c r="H179" s="35"/>
+      <c r="I179" s="36" t="s">
         <v>361</v>
       </c>
       <c r="J179" s="6" t="s">
@@ -9793,8 +9865,8 @@
       <c r="G180" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H180" s="32"/>
-      <c r="I180" s="37" t="s">
+      <c r="H180" s="35"/>
+      <c r="I180" s="36" t="s">
         <v>363</v>
       </c>
       <c r="J180" s="6" t="s">
@@ -9820,8 +9892,8 @@
       <c r="G181" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H181" s="32"/>
-      <c r="I181" s="37" t="s">
+      <c r="H181" s="35"/>
+      <c r="I181" s="36" t="s">
         <v>365</v>
       </c>
       <c r="J181" s="6" t="s">
@@ -9847,8 +9919,8 @@
       <c r="G182" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H182" s="32"/>
-      <c r="I182" s="37" t="s">
+      <c r="H182" s="35"/>
+      <c r="I182" s="36" t="s">
         <v>367</v>
       </c>
       <c r="J182" s="6" t="s">
@@ -9874,8 +9946,8 @@
       <c r="G183" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H183" s="32"/>
-      <c r="I183" s="37" t="s">
+      <c r="H183" s="35"/>
+      <c r="I183" s="36" t="s">
         <v>369</v>
       </c>
       <c r="J183" s="6" t="s">
@@ -9883,15 +9955,15 @@
       </c>
     </row>
     <row r="184" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B184" s="33"/>
-      <c r="C184" s="33"/>
-      <c r="D184" s="33"/>
-      <c r="E184" s="33"/>
-      <c r="F184" s="33"/>
-      <c r="G184" s="33"/>
-      <c r="H184" s="33"/>
-      <c r="I184" s="33"/>
-      <c r="J184" s="33"/>
+      <c r="B184" s="39"/>
+      <c r="C184" s="39"/>
+      <c r="D184" s="39"/>
+      <c r="E184" s="39"/>
+      <c r="F184" s="39"/>
+      <c r="G184" s="39"/>
+      <c r="H184" s="39"/>
+      <c r="I184" s="39"/>
+      <c r="J184" s="39"/>
     </row>
     <row r="185" ht="37.5" customHeight="1" spans="2:10">
       <c r="B185" s="54">
@@ -9912,8 +9984,8 @@
       <c r="G185" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H185" s="32"/>
-      <c r="I185" s="37" t="s">
+      <c r="H185" s="35"/>
+      <c r="I185" s="36" t="s">
         <v>371</v>
       </c>
       <c r="J185" s="6" t="s">
@@ -9939,8 +10011,8 @@
       <c r="G186" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H186" s="32"/>
-      <c r="I186" s="37" t="s">
+      <c r="H186" s="35"/>
+      <c r="I186" s="36" t="s">
         <v>373</v>
       </c>
       <c r="J186" s="6" t="s">
@@ -9966,8 +10038,8 @@
       <c r="G187" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H187" s="32"/>
-      <c r="I187" s="37" t="s">
+      <c r="H187" s="35"/>
+      <c r="I187" s="36" t="s">
         <v>375</v>
       </c>
       <c r="J187" s="6" t="s">
@@ -9993,8 +10065,8 @@
       <c r="G188" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H188" s="32"/>
-      <c r="I188" s="37" t="s">
+      <c r="H188" s="35"/>
+      <c r="I188" s="36" t="s">
         <v>377</v>
       </c>
       <c r="J188" s="6" t="s">
@@ -10020,8 +10092,8 @@
       <c r="G189" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H189" s="32"/>
-      <c r="I189" s="37" t="s">
+      <c r="H189" s="35"/>
+      <c r="I189" s="36" t="s">
         <v>379</v>
       </c>
       <c r="J189" s="6" t="s">
@@ -10047,8 +10119,8 @@
       <c r="G190" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H190" s="32"/>
-      <c r="I190" s="37" t="s">
+      <c r="H190" s="35"/>
+      <c r="I190" s="36" t="s">
         <v>381</v>
       </c>
       <c r="J190" s="6" t="s">
@@ -10074,8 +10146,8 @@
       <c r="G191" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H191" s="32"/>
-      <c r="I191" s="37" t="s">
+      <c r="H191" s="35"/>
+      <c r="I191" s="36" t="s">
         <v>383</v>
       </c>
       <c r="J191" s="6" t="s">
@@ -10083,15 +10155,15 @@
       </c>
     </row>
     <row r="192" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B192" s="33"/>
-      <c r="C192" s="33"/>
-      <c r="D192" s="33"/>
-      <c r="E192" s="33"/>
-      <c r="F192" s="33"/>
-      <c r="G192" s="33"/>
-      <c r="H192" s="33"/>
-      <c r="I192" s="33"/>
-      <c r="J192" s="33"/>
+      <c r="B192" s="39"/>
+      <c r="C192" s="39"/>
+      <c r="D192" s="39"/>
+      <c r="E192" s="39"/>
+      <c r="F192" s="39"/>
+      <c r="G192" s="39"/>
+      <c r="H192" s="39"/>
+      <c r="I192" s="39"/>
+      <c r="J192" s="39"/>
     </row>
     <row r="193" ht="37.5" customHeight="1" spans="2:10">
       <c r="B193" s="54">
@@ -10112,8 +10184,8 @@
       <c r="G193" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H193" s="32"/>
-      <c r="I193" s="37" t="s">
+      <c r="H193" s="35"/>
+      <c r="I193" s="36" t="s">
         <v>385</v>
       </c>
       <c r="J193" s="6" t="s">
@@ -10139,8 +10211,8 @@
       <c r="G194" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H194" s="32"/>
-      <c r="I194" s="37" t="s">
+      <c r="H194" s="35"/>
+      <c r="I194" s="36" t="s">
         <v>387</v>
       </c>
       <c r="J194" s="6" t="s">
@@ -10166,8 +10238,8 @@
       <c r="G195" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H195" s="32"/>
-      <c r="I195" s="37" t="s">
+      <c r="H195" s="35"/>
+      <c r="I195" s="36" t="s">
         <v>389</v>
       </c>
       <c r="J195" s="6" t="s">
@@ -10193,8 +10265,8 @@
       <c r="G196" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H196" s="32"/>
-      <c r="I196" s="37" t="s">
+      <c r="H196" s="35"/>
+      <c r="I196" s="36" t="s">
         <v>391</v>
       </c>
       <c r="J196" s="6" t="s">
@@ -10220,8 +10292,8 @@
       <c r="G197" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H197" s="32"/>
-      <c r="I197" s="37" t="s">
+      <c r="H197" s="35"/>
+      <c r="I197" s="36" t="s">
         <v>393</v>
       </c>
       <c r="J197" s="6" t="s">
@@ -10247,8 +10319,8 @@
       <c r="G198" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H198" s="32"/>
-      <c r="I198" s="37" t="s">
+      <c r="H198" s="35"/>
+      <c r="I198" s="36" t="s">
         <v>395</v>
       </c>
       <c r="J198" s="6" t="s">
@@ -10274,8 +10346,8 @@
       <c r="G199" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="H199" s="32"/>
-      <c r="I199" s="37" t="s">
+      <c r="H199" s="35"/>
+      <c r="I199" s="36" t="s">
         <v>397</v>
       </c>
       <c r="J199" s="6" t="s">
@@ -10283,15 +10355,15 @@
       </c>
     </row>
     <row r="200" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B200" s="33"/>
-      <c r="C200" s="33"/>
-      <c r="D200" s="33"/>
-      <c r="E200" s="33"/>
-      <c r="F200" s="33"/>
-      <c r="G200" s="33"/>
-      <c r="H200" s="33"/>
-      <c r="I200" s="33"/>
-      <c r="J200" s="33"/>
+      <c r="B200" s="39"/>
+      <c r="C200" s="39"/>
+      <c r="D200" s="39"/>
+      <c r="E200" s="39"/>
+      <c r="F200" s="39"/>
+      <c r="G200" s="39"/>
+      <c r="H200" s="39"/>
+      <c r="I200" s="39"/>
+      <c r="J200" s="39"/>
     </row>
     <row r="201" ht="13.5" customHeight="1" spans="2:10">
       <c r="B201" s="59" t="s">
@@ -10336,8 +10408,8 @@
       <c r="G203" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H203" s="32"/>
-      <c r="I203" s="37" t="s">
+      <c r="H203" s="35"/>
+      <c r="I203" s="36" t="s">
         <v>400</v>
       </c>
       <c r="J203" s="6" t="s">
@@ -10363,8 +10435,8 @@
       <c r="G204" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H204" s="32"/>
-      <c r="I204" s="37" t="s">
+      <c r="H204" s="35"/>
+      <c r="I204" s="36" t="s">
         <v>403</v>
       </c>
       <c r="J204" s="6" t="s">
@@ -10390,8 +10462,8 @@
       <c r="G205" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H205" s="32"/>
-      <c r="I205" s="37" t="s">
+      <c r="H205" s="35"/>
+      <c r="I205" s="36" t="s">
         <v>405</v>
       </c>
       <c r="J205" s="6" t="s">
@@ -10417,8 +10489,8 @@
       <c r="G206" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H206" s="32"/>
-      <c r="I206" s="37" t="s">
+      <c r="H206" s="35"/>
+      <c r="I206" s="36" t="s">
         <v>407</v>
       </c>
       <c r="J206" s="6" t="s">
@@ -10444,8 +10516,8 @@
       <c r="G207" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H207" s="32"/>
-      <c r="I207" s="37" t="s">
+      <c r="H207" s="35"/>
+      <c r="I207" s="36" t="s">
         <v>409</v>
       </c>
       <c r="J207" s="6" t="s">
@@ -10471,8 +10543,8 @@
       <c r="G208" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H208" s="32"/>
-      <c r="I208" s="37" t="s">
+      <c r="H208" s="35"/>
+      <c r="I208" s="36" t="s">
         <v>411</v>
       </c>
       <c r="J208" s="6" t="s">
@@ -10498,8 +10570,8 @@
       <c r="G209" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H209" s="32"/>
-      <c r="I209" s="37" t="s">
+      <c r="H209" s="35"/>
+      <c r="I209" s="36" t="s">
         <v>413</v>
       </c>
       <c r="J209" s="6" t="s">
@@ -10507,15 +10579,15 @@
       </c>
     </row>
     <row r="210" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B210" s="33"/>
-      <c r="C210" s="33"/>
-      <c r="D210" s="33"/>
-      <c r="E210" s="33"/>
-      <c r="F210" s="33"/>
-      <c r="G210" s="33"/>
-      <c r="H210" s="33"/>
-      <c r="I210" s="33"/>
-      <c r="J210" s="33"/>
+      <c r="B210" s="39"/>
+      <c r="C210" s="39"/>
+      <c r="D210" s="39"/>
+      <c r="E210" s="39"/>
+      <c r="F210" s="39"/>
+      <c r="G210" s="39"/>
+      <c r="H210" s="39"/>
+      <c r="I210" s="39"/>
+      <c r="J210" s="39"/>
     </row>
     <row r="211" ht="37.5" customHeight="1" spans="2:10">
       <c r="B211" s="60">
@@ -10536,8 +10608,8 @@
       <c r="G211" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H211" s="32"/>
-      <c r="I211" s="37" t="s">
+      <c r="H211" s="35"/>
+      <c r="I211" s="36" t="s">
         <v>415</v>
       </c>
       <c r="J211" s="6" t="s">
@@ -10563,8 +10635,8 @@
       <c r="G212" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H212" s="32"/>
-      <c r="I212" s="37" t="s">
+      <c r="H212" s="35"/>
+      <c r="I212" s="36" t="s">
         <v>417</v>
       </c>
       <c r="J212" s="6" t="s">
@@ -10590,8 +10662,8 @@
       <c r="G213" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H213" s="32"/>
-      <c r="I213" s="37" t="s">
+      <c r="H213" s="35"/>
+      <c r="I213" s="36" t="s">
         <v>419</v>
       </c>
       <c r="J213" s="6" t="s">
@@ -10617,8 +10689,8 @@
       <c r="G214" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H214" s="32"/>
-      <c r="I214" s="37" t="s">
+      <c r="H214" s="35"/>
+      <c r="I214" s="36" t="s">
         <v>421</v>
       </c>
       <c r="J214" s="6" t="s">
@@ -10644,8 +10716,8 @@
       <c r="G215" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H215" s="32"/>
-      <c r="I215" s="37" t="s">
+      <c r="H215" s="35"/>
+      <c r="I215" s="36" t="s">
         <v>423</v>
       </c>
       <c r="J215" s="6" t="s">
@@ -10671,8 +10743,8 @@
       <c r="G216" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H216" s="32"/>
-      <c r="I216" s="37" t="s">
+      <c r="H216" s="35"/>
+      <c r="I216" s="36" t="s">
         <v>425</v>
       </c>
       <c r="J216" s="6" t="s">
@@ -10698,8 +10770,8 @@
       <c r="G217" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H217" s="32"/>
-      <c r="I217" s="37" t="s">
+      <c r="H217" s="35"/>
+      <c r="I217" s="36" t="s">
         <v>427</v>
       </c>
       <c r="J217" s="6" t="s">
@@ -10707,15 +10779,15 @@
       </c>
     </row>
     <row r="218" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B218" s="33"/>
-      <c r="C218" s="33"/>
-      <c r="D218" s="33"/>
-      <c r="E218" s="33"/>
-      <c r="F218" s="33"/>
-      <c r="G218" s="33"/>
-      <c r="H218" s="33"/>
-      <c r="I218" s="33"/>
-      <c r="J218" s="33"/>
+      <c r="B218" s="39"/>
+      <c r="C218" s="39"/>
+      <c r="D218" s="39"/>
+      <c r="E218" s="39"/>
+      <c r="F218" s="39"/>
+      <c r="G218" s="39"/>
+      <c r="H218" s="39"/>
+      <c r="I218" s="39"/>
+      <c r="J218" s="39"/>
     </row>
     <row r="219" ht="37.5" customHeight="1" spans="2:10">
       <c r="B219" s="60">
@@ -10736,8 +10808,8 @@
       <c r="G219" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H219" s="32"/>
-      <c r="I219" s="37" t="s">
+      <c r="H219" s="35"/>
+      <c r="I219" s="36" t="s">
         <v>429</v>
       </c>
       <c r="J219" s="6" t="s">
@@ -10763,8 +10835,8 @@
       <c r="G220" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H220" s="32"/>
-      <c r="I220" s="37" t="s">
+      <c r="H220" s="35"/>
+      <c r="I220" s="36" t="s">
         <v>431</v>
       </c>
       <c r="J220" s="6" t="s">
@@ -10790,8 +10862,8 @@
       <c r="G221" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H221" s="32"/>
-      <c r="I221" s="37" t="s">
+      <c r="H221" s="35"/>
+      <c r="I221" s="36" t="s">
         <v>433</v>
       </c>
       <c r="J221" s="6" t="s">
@@ -10817,8 +10889,8 @@
       <c r="G222" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H222" s="32"/>
-      <c r="I222" s="37" t="s">
+      <c r="H222" s="35"/>
+      <c r="I222" s="36" t="s">
         <v>435</v>
       </c>
       <c r="J222" s="6" t="s">
@@ -10844,8 +10916,8 @@
       <c r="G223" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H223" s="32"/>
-      <c r="I223" s="37" t="s">
+      <c r="H223" s="35"/>
+      <c r="I223" s="36" t="s">
         <v>437</v>
       </c>
       <c r="J223" s="6" t="s">
@@ -10871,8 +10943,8 @@
       <c r="G224" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H224" s="32"/>
-      <c r="I224" s="37" t="s">
+      <c r="H224" s="35"/>
+      <c r="I224" s="36" t="s">
         <v>439</v>
       </c>
       <c r="J224" s="6" t="s">
@@ -10898,8 +10970,8 @@
       <c r="G225" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H225" s="32"/>
-      <c r="I225" s="37" t="s">
+      <c r="H225" s="35"/>
+      <c r="I225" s="36" t="s">
         <v>441</v>
       </c>
       <c r="J225" s="6" t="s">
@@ -10907,15 +10979,15 @@
       </c>
     </row>
     <row r="226" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B226" s="33"/>
-      <c r="C226" s="33"/>
-      <c r="D226" s="33"/>
-      <c r="E226" s="33"/>
-      <c r="F226" s="33"/>
-      <c r="G226" s="33"/>
-      <c r="H226" s="33"/>
-      <c r="I226" s="33"/>
-      <c r="J226" s="33"/>
+      <c r="B226" s="39"/>
+      <c r="C226" s="39"/>
+      <c r="D226" s="39"/>
+      <c r="E226" s="39"/>
+      <c r="F226" s="39"/>
+      <c r="G226" s="39"/>
+      <c r="H226" s="39"/>
+      <c r="I226" s="39"/>
+      <c r="J226" s="39"/>
     </row>
     <row r="227" ht="37.5" customHeight="1" spans="2:10">
       <c r="B227" s="60">
@@ -10936,8 +11008,8 @@
       <c r="G227" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H227" s="32"/>
-      <c r="I227" s="37" t="s">
+      <c r="H227" s="35"/>
+      <c r="I227" s="36" t="s">
         <v>443</v>
       </c>
       <c r="J227" s="6" t="s">
@@ -10963,8 +11035,8 @@
       <c r="G228" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H228" s="32"/>
-      <c r="I228" s="37" t="s">
+      <c r="H228" s="35"/>
+      <c r="I228" s="36" t="s">
         <v>445</v>
       </c>
       <c r="J228" s="6" t="s">
@@ -10990,8 +11062,8 @@
       <c r="G229" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H229" s="32"/>
-      <c r="I229" s="37" t="s">
+      <c r="H229" s="35"/>
+      <c r="I229" s="36" t="s">
         <v>447</v>
       </c>
       <c r="J229" s="6" t="s">
@@ -11017,8 +11089,8 @@
       <c r="G230" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H230" s="32"/>
-      <c r="I230" s="37" t="s">
+      <c r="H230" s="35"/>
+      <c r="I230" s="36" t="s">
         <v>449</v>
       </c>
       <c r="J230" s="6" t="s">
@@ -11044,8 +11116,8 @@
       <c r="G231" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H231" s="32"/>
-      <c r="I231" s="37" t="s">
+      <c r="H231" s="35"/>
+      <c r="I231" s="36" t="s">
         <v>451</v>
       </c>
       <c r="J231" s="6" t="s">
@@ -11071,8 +11143,8 @@
       <c r="G232" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H232" s="32"/>
-      <c r="I232" s="37" t="s">
+      <c r="H232" s="35"/>
+      <c r="I232" s="36" t="s">
         <v>453</v>
       </c>
       <c r="J232" s="6" t="s">
@@ -11098,8 +11170,8 @@
       <c r="G233" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H233" s="32"/>
-      <c r="I233" s="37" t="s">
+      <c r="H233" s="35"/>
+      <c r="I233" s="36" t="s">
         <v>455</v>
       </c>
       <c r="J233" s="6" t="s">
@@ -11107,15 +11179,15 @@
       </c>
     </row>
     <row r="234" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B234" s="33"/>
-      <c r="C234" s="33"/>
-      <c r="D234" s="33"/>
-      <c r="E234" s="33"/>
-      <c r="F234" s="33"/>
-      <c r="G234" s="33"/>
-      <c r="H234" s="33"/>
-      <c r="I234" s="33"/>
-      <c r="J234" s="33"/>
+      <c r="B234" s="39"/>
+      <c r="C234" s="39"/>
+      <c r="D234" s="39"/>
+      <c r="E234" s="39"/>
+      <c r="F234" s="39"/>
+      <c r="G234" s="39"/>
+      <c r="H234" s="39"/>
+      <c r="I234" s="39"/>
+      <c r="J234" s="39"/>
     </row>
     <row r="235" ht="37.5" customHeight="1" spans="2:10">
       <c r="B235" s="60">
@@ -11136,8 +11208,8 @@
       <c r="G235" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H235" s="32"/>
-      <c r="I235" s="37" t="s">
+      <c r="H235" s="35"/>
+      <c r="I235" s="36" t="s">
         <v>457</v>
       </c>
       <c r="J235" s="6" t="s">
@@ -11163,8 +11235,8 @@
       <c r="G236" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H236" s="32"/>
-      <c r="I236" s="37" t="s">
+      <c r="H236" s="35"/>
+      <c r="I236" s="36" t="s">
         <v>459</v>
       </c>
       <c r="J236" s="6" t="s">
@@ -11190,8 +11262,8 @@
       <c r="G237" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H237" s="32"/>
-      <c r="I237" s="37" t="s">
+      <c r="H237" s="35"/>
+      <c r="I237" s="36" t="s">
         <v>461</v>
       </c>
       <c r="J237" s="6" t="s">
@@ -11217,8 +11289,8 @@
       <c r="G238" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H238" s="32"/>
-      <c r="I238" s="37" t="s">
+      <c r="H238" s="35"/>
+      <c r="I238" s="36" t="s">
         <v>463</v>
       </c>
       <c r="J238" s="6" t="s">
@@ -11244,8 +11316,8 @@
       <c r="G239" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H239" s="32"/>
-      <c r="I239" s="37" t="s">
+      <c r="H239" s="35"/>
+      <c r="I239" s="36" t="s">
         <v>465</v>
       </c>
       <c r="J239" s="6" t="s">
@@ -11271,8 +11343,8 @@
       <c r="G240" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H240" s="32"/>
-      <c r="I240" s="37" t="s">
+      <c r="H240" s="35"/>
+      <c r="I240" s="36" t="s">
         <v>467</v>
       </c>
       <c r="J240" s="6" t="s">
@@ -11298,8 +11370,8 @@
       <c r="G241" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H241" s="32"/>
-      <c r="I241" s="37" t="s">
+      <c r="H241" s="35"/>
+      <c r="I241" s="36" t="s">
         <v>469</v>
       </c>
       <c r="J241" s="6" t="s">
@@ -11307,15 +11379,15 @@
       </c>
     </row>
     <row r="242" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B242" s="33"/>
-      <c r="C242" s="33"/>
-      <c r="D242" s="33"/>
-      <c r="E242" s="33"/>
-      <c r="F242" s="33"/>
-      <c r="G242" s="33"/>
-      <c r="H242" s="33"/>
-      <c r="I242" s="33"/>
-      <c r="J242" s="33"/>
+      <c r="B242" s="39"/>
+      <c r="C242" s="39"/>
+      <c r="D242" s="39"/>
+      <c r="E242" s="39"/>
+      <c r="F242" s="39"/>
+      <c r="G242" s="39"/>
+      <c r="H242" s="39"/>
+      <c r="I242" s="39"/>
+      <c r="J242" s="39"/>
     </row>
     <row r="243" ht="37.5" customHeight="1" spans="2:10">
       <c r="B243" s="60">
@@ -11336,8 +11408,8 @@
       <c r="G243" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H243" s="32"/>
-      <c r="I243" s="37" t="s">
+      <c r="H243" s="35"/>
+      <c r="I243" s="36" t="s">
         <v>471</v>
       </c>
       <c r="J243" s="6" t="s">
@@ -11363,8 +11435,8 @@
       <c r="G244" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H244" s="32"/>
-      <c r="I244" s="37" t="s">
+      <c r="H244" s="35"/>
+      <c r="I244" s="36" t="s">
         <v>473</v>
       </c>
       <c r="J244" s="6" t="s">
@@ -11390,8 +11462,8 @@
       <c r="G245" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H245" s="32"/>
-      <c r="I245" s="37" t="s">
+      <c r="H245" s="35"/>
+      <c r="I245" s="36" t="s">
         <v>475</v>
       </c>
       <c r="J245" s="6" t="s">
@@ -11417,8 +11489,8 @@
       <c r="G246" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H246" s="32"/>
-      <c r="I246" s="37" t="s">
+      <c r="H246" s="35"/>
+      <c r="I246" s="36" t="s">
         <v>477</v>
       </c>
       <c r="J246" s="6" t="s">
@@ -11444,8 +11516,8 @@
       <c r="G247" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H247" s="32"/>
-      <c r="I247" s="37" t="s">
+      <c r="H247" s="35"/>
+      <c r="I247" s="36" t="s">
         <v>479</v>
       </c>
       <c r="J247" s="6" t="s">
@@ -11471,8 +11543,8 @@
       <c r="G248" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H248" s="32"/>
-      <c r="I248" s="37" t="s">
+      <c r="H248" s="35"/>
+      <c r="I248" s="36" t="s">
         <v>481</v>
       </c>
       <c r="J248" s="6" t="s">
@@ -11498,8 +11570,8 @@
       <c r="G249" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H249" s="32"/>
-      <c r="I249" s="37" t="s">
+      <c r="H249" s="35"/>
+      <c r="I249" s="36" t="s">
         <v>483</v>
       </c>
       <c r="J249" s="6" t="s">
@@ -11507,15 +11579,15 @@
       </c>
     </row>
     <row r="250" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B250" s="33"/>
-      <c r="C250" s="33"/>
-      <c r="D250" s="33"/>
-      <c r="E250" s="33"/>
-      <c r="F250" s="33"/>
-      <c r="G250" s="33"/>
-      <c r="H250" s="33"/>
-      <c r="I250" s="33"/>
-      <c r="J250" s="33"/>
+      <c r="B250" s="39"/>
+      <c r="C250" s="39"/>
+      <c r="D250" s="39"/>
+      <c r="E250" s="39"/>
+      <c r="F250" s="39"/>
+      <c r="G250" s="39"/>
+      <c r="H250" s="39"/>
+      <c r="I250" s="39"/>
+      <c r="J250" s="39"/>
     </row>
     <row r="251" ht="37.5" customHeight="1" spans="2:10">
       <c r="B251" s="60">
@@ -11536,8 +11608,8 @@
       <c r="G251" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H251" s="32"/>
-      <c r="I251" s="37" t="s">
+      <c r="H251" s="35"/>
+      <c r="I251" s="36" t="s">
         <v>485</v>
       </c>
       <c r="J251" s="6" t="s">
@@ -11563,8 +11635,8 @@
       <c r="G252" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H252" s="32"/>
-      <c r="I252" s="37" t="s">
+      <c r="H252" s="35"/>
+      <c r="I252" s="36" t="s">
         <v>487</v>
       </c>
       <c r="J252" s="6" t="s">
@@ -11590,8 +11662,8 @@
       <c r="G253" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H253" s="32"/>
-      <c r="I253" s="37" t="s">
+      <c r="H253" s="35"/>
+      <c r="I253" s="36" t="s">
         <v>489</v>
       </c>
       <c r="J253" s="6" t="s">
@@ -11617,8 +11689,8 @@
       <c r="G254" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H254" s="32"/>
-      <c r="I254" s="37" t="s">
+      <c r="H254" s="35"/>
+      <c r="I254" s="36" t="s">
         <v>491</v>
       </c>
       <c r="J254" s="6" t="s">
@@ -11644,8 +11716,8 @@
       <c r="G255" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H255" s="32"/>
-      <c r="I255" s="37" t="s">
+      <c r="H255" s="35"/>
+      <c r="I255" s="36" t="s">
         <v>493</v>
       </c>
       <c r="J255" s="6" t="s">
@@ -11671,8 +11743,8 @@
       <c r="G256" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H256" s="32"/>
-      <c r="I256" s="37" t="s">
+      <c r="H256" s="35"/>
+      <c r="I256" s="36" t="s">
         <v>495</v>
       </c>
       <c r="J256" s="6" t="s">
@@ -11698,8 +11770,8 @@
       <c r="G257" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H257" s="32"/>
-      <c r="I257" s="37" t="s">
+      <c r="H257" s="35"/>
+      <c r="I257" s="36" t="s">
         <v>497</v>
       </c>
       <c r="J257" s="6" t="s">
@@ -11707,15 +11779,15 @@
       </c>
     </row>
     <row r="258" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B258" s="33"/>
-      <c r="C258" s="33"/>
-      <c r="D258" s="33"/>
-      <c r="E258" s="33"/>
-      <c r="F258" s="33"/>
-      <c r="G258" s="33"/>
-      <c r="H258" s="33"/>
-      <c r="I258" s="33"/>
-      <c r="J258" s="33"/>
+      <c r="B258" s="39"/>
+      <c r="C258" s="39"/>
+      <c r="D258" s="39"/>
+      <c r="E258" s="39"/>
+      <c r="F258" s="39"/>
+      <c r="G258" s="39"/>
+      <c r="H258" s="39"/>
+      <c r="I258" s="39"/>
+      <c r="J258" s="39"/>
     </row>
     <row r="259" ht="37.5" customHeight="1" spans="2:10">
       <c r="B259" s="60">
@@ -11736,8 +11808,8 @@
       <c r="G259" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H259" s="32"/>
-      <c r="I259" s="37" t="s">
+      <c r="H259" s="35"/>
+      <c r="I259" s="36" t="s">
         <v>499</v>
       </c>
       <c r="J259" s="6" t="s">
@@ -11763,8 +11835,8 @@
       <c r="G260" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H260" s="32"/>
-      <c r="I260" s="37" t="s">
+      <c r="H260" s="35"/>
+      <c r="I260" s="36" t="s">
         <v>501</v>
       </c>
       <c r="J260" s="6" t="s">
@@ -11790,8 +11862,8 @@
       <c r="G261" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H261" s="32"/>
-      <c r="I261" s="37" t="s">
+      <c r="H261" s="35"/>
+      <c r="I261" s="36" t="s">
         <v>503</v>
       </c>
       <c r="J261" s="6" t="s">
@@ -11817,8 +11889,8 @@
       <c r="G262" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H262" s="32"/>
-      <c r="I262" s="37" t="s">
+      <c r="H262" s="35"/>
+      <c r="I262" s="36" t="s">
         <v>505</v>
       </c>
       <c r="J262" s="6" t="s">
@@ -11844,8 +11916,8 @@
       <c r="G263" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H263" s="32"/>
-      <c r="I263" s="37" t="s">
+      <c r="H263" s="35"/>
+      <c r="I263" s="36" t="s">
         <v>507</v>
       </c>
       <c r="J263" s="6" t="s">
@@ -11871,8 +11943,8 @@
       <c r="G264" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H264" s="32"/>
-      <c r="I264" s="37" t="s">
+      <c r="H264" s="35"/>
+      <c r="I264" s="36" t="s">
         <v>509</v>
       </c>
       <c r="J264" s="6" t="s">
@@ -11898,8 +11970,8 @@
       <c r="G265" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="H265" s="32"/>
-      <c r="I265" s="37" t="s">
+      <c r="H265" s="35"/>
+      <c r="I265" s="36" t="s">
         <v>511</v>
       </c>
       <c r="J265" s="6" t="s">
@@ -11907,15 +11979,15 @@
       </c>
     </row>
     <row r="266" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B266" s="33"/>
-      <c r="C266" s="33"/>
-      <c r="D266" s="33"/>
-      <c r="E266" s="33"/>
-      <c r="F266" s="33"/>
-      <c r="G266" s="33"/>
-      <c r="H266" s="33"/>
-      <c r="I266" s="33"/>
-      <c r="J266" s="33"/>
+      <c r="B266" s="39"/>
+      <c r="C266" s="39"/>
+      <c r="D266" s="39"/>
+      <c r="E266" s="39"/>
+      <c r="F266" s="39"/>
+      <c r="G266" s="39"/>
+      <c r="H266" s="39"/>
+      <c r="I266" s="39"/>
+      <c r="J266" s="39"/>
     </row>
     <row r="267" ht="13.5" customHeight="1" spans="2:10">
       <c r="B267" s="65" t="s">
@@ -11960,8 +12032,8 @@
       <c r="G269" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H269" s="32"/>
-      <c r="I269" s="37" t="s">
+      <c r="H269" s="35"/>
+      <c r="I269" s="36" t="s">
         <v>514</v>
       </c>
       <c r="J269" s="6" t="s">
@@ -11987,8 +12059,8 @@
       <c r="G270" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H270" s="32"/>
-      <c r="I270" s="37" t="s">
+      <c r="H270" s="35"/>
+      <c r="I270" s="36" t="s">
         <v>517</v>
       </c>
       <c r="J270" s="6" t="s">
@@ -12014,8 +12086,8 @@
       <c r="G271" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H271" s="32"/>
-      <c r="I271" s="37" t="s">
+      <c r="H271" s="35"/>
+      <c r="I271" s="36" t="s">
         <v>519</v>
       </c>
       <c r="J271" s="6" t="s">
@@ -12041,8 +12113,8 @@
       <c r="G272" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H272" s="32"/>
-      <c r="I272" s="37" t="s">
+      <c r="H272" s="35"/>
+      <c r="I272" s="36" t="s">
         <v>521</v>
       </c>
       <c r="J272" s="6" t="s">
@@ -12068,8 +12140,8 @@
       <c r="G273" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H273" s="32"/>
-      <c r="I273" s="37" t="s">
+      <c r="H273" s="35"/>
+      <c r="I273" s="36" t="s">
         <v>523</v>
       </c>
       <c r="J273" s="6" t="s">
@@ -12095,8 +12167,8 @@
       <c r="G274" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H274" s="32"/>
-      <c r="I274" s="37" t="s">
+      <c r="H274" s="35"/>
+      <c r="I274" s="36" t="s">
         <v>525</v>
       </c>
       <c r="J274" s="6" t="s">
@@ -12122,8 +12194,8 @@
       <c r="G275" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H275" s="32"/>
-      <c r="I275" s="37" t="s">
+      <c r="H275" s="35"/>
+      <c r="I275" s="36" t="s">
         <v>527</v>
       </c>
       <c r="J275" s="6" t="s">
@@ -12131,15 +12203,15 @@
       </c>
     </row>
     <row r="276" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B276" s="33"/>
-      <c r="C276" s="33"/>
-      <c r="D276" s="33"/>
-      <c r="E276" s="33"/>
-      <c r="F276" s="33"/>
-      <c r="G276" s="33"/>
-      <c r="H276" s="33"/>
-      <c r="I276" s="33"/>
-      <c r="J276" s="33"/>
+      <c r="B276" s="39"/>
+      <c r="C276" s="39"/>
+      <c r="D276" s="39"/>
+      <c r="E276" s="39"/>
+      <c r="F276" s="39"/>
+      <c r="G276" s="39"/>
+      <c r="H276" s="39"/>
+      <c r="I276" s="39"/>
+      <c r="J276" s="39"/>
     </row>
     <row r="277" ht="37.5" customHeight="1" spans="2:10">
       <c r="B277" s="66">
@@ -12160,8 +12232,8 @@
       <c r="G277" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H277" s="32"/>
-      <c r="I277" s="37" t="s">
+      <c r="H277" s="35"/>
+      <c r="I277" s="36" t="s">
         <v>529</v>
       </c>
       <c r="J277" s="6" t="s">
@@ -12187,8 +12259,8 @@
       <c r="G278" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H278" s="32"/>
-      <c r="I278" s="37" t="s">
+      <c r="H278" s="35"/>
+      <c r="I278" s="36" t="s">
         <v>531</v>
       </c>
       <c r="J278" s="6" t="s">
@@ -12214,8 +12286,8 @@
       <c r="G279" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H279" s="32"/>
-      <c r="I279" s="37" t="s">
+      <c r="H279" s="35"/>
+      <c r="I279" s="36" t="s">
         <v>533</v>
       </c>
       <c r="J279" s="6" t="s">
@@ -12241,8 +12313,8 @@
       <c r="G280" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H280" s="32"/>
-      <c r="I280" s="37" t="s">
+      <c r="H280" s="35"/>
+      <c r="I280" s="36" t="s">
         <v>535</v>
       </c>
       <c r="J280" s="6" t="s">
@@ -12268,8 +12340,8 @@
       <c r="G281" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H281" s="32"/>
-      <c r="I281" s="37" t="s">
+      <c r="H281" s="35"/>
+      <c r="I281" s="36" t="s">
         <v>537</v>
       </c>
       <c r="J281" s="6" t="s">
@@ -12295,8 +12367,8 @@
       <c r="G282" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H282" s="32"/>
-      <c r="I282" s="37" t="s">
+      <c r="H282" s="35"/>
+      <c r="I282" s="36" t="s">
         <v>539</v>
       </c>
       <c r="J282" s="6" t="s">
@@ -12322,8 +12394,8 @@
       <c r="G283" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H283" s="32"/>
-      <c r="I283" s="37" t="s">
+      <c r="H283" s="35"/>
+      <c r="I283" s="36" t="s">
         <v>541</v>
       </c>
       <c r="J283" s="6" t="s">
@@ -12331,15 +12403,15 @@
       </c>
     </row>
     <row r="284" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B284" s="33"/>
-      <c r="C284" s="33"/>
-      <c r="D284" s="33"/>
-      <c r="E284" s="33"/>
-      <c r="F284" s="33"/>
-      <c r="G284" s="33"/>
-      <c r="H284" s="33"/>
-      <c r="I284" s="33"/>
-      <c r="J284" s="33"/>
+      <c r="B284" s="39"/>
+      <c r="C284" s="39"/>
+      <c r="D284" s="39"/>
+      <c r="E284" s="39"/>
+      <c r="F284" s="39"/>
+      <c r="G284" s="39"/>
+      <c r="H284" s="39"/>
+      <c r="I284" s="39"/>
+      <c r="J284" s="39"/>
     </row>
     <row r="285" ht="37.5" customHeight="1" spans="2:10">
       <c r="B285" s="66">
@@ -12360,8 +12432,8 @@
       <c r="G285" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H285" s="32"/>
-      <c r="I285" s="37" t="s">
+      <c r="H285" s="35"/>
+      <c r="I285" s="36" t="s">
         <v>543</v>
       </c>
       <c r="J285" s="6" t="s">
@@ -12387,8 +12459,8 @@
       <c r="G286" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H286" s="32"/>
-      <c r="I286" s="37" t="s">
+      <c r="H286" s="35"/>
+      <c r="I286" s="36" t="s">
         <v>545</v>
       </c>
       <c r="J286" s="6" t="s">
@@ -12414,8 +12486,8 @@
       <c r="G287" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H287" s="32"/>
-      <c r="I287" s="37" t="s">
+      <c r="H287" s="35"/>
+      <c r="I287" s="36" t="s">
         <v>547</v>
       </c>
       <c r="J287" s="6" t="s">
@@ -12441,8 +12513,8 @@
       <c r="G288" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H288" s="32"/>
-      <c r="I288" s="37" t="s">
+      <c r="H288" s="35"/>
+      <c r="I288" s="36" t="s">
         <v>549</v>
       </c>
       <c r="J288" s="6" t="s">
@@ -12468,8 +12540,8 @@
       <c r="G289" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H289" s="32"/>
-      <c r="I289" s="37" t="s">
+      <c r="H289" s="35"/>
+      <c r="I289" s="36" t="s">
         <v>551</v>
       </c>
       <c r="J289" s="6" t="s">
@@ -12495,8 +12567,8 @@
       <c r="G290" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H290" s="32"/>
-      <c r="I290" s="37" t="s">
+      <c r="H290" s="35"/>
+      <c r="I290" s="36" t="s">
         <v>553</v>
       </c>
       <c r="J290" s="6" t="s">
@@ -12522,8 +12594,8 @@
       <c r="G291" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H291" s="32"/>
-      <c r="I291" s="37" t="s">
+      <c r="H291" s="35"/>
+      <c r="I291" s="36" t="s">
         <v>555</v>
       </c>
       <c r="J291" s="6" t="s">
@@ -12531,15 +12603,15 @@
       </c>
     </row>
     <row r="292" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B292" s="33"/>
-      <c r="C292" s="33"/>
-      <c r="D292" s="33"/>
-      <c r="E292" s="33"/>
-      <c r="F292" s="33"/>
-      <c r="G292" s="33"/>
-      <c r="H292" s="33"/>
-      <c r="I292" s="33"/>
-      <c r="J292" s="33"/>
+      <c r="B292" s="39"/>
+      <c r="C292" s="39"/>
+      <c r="D292" s="39"/>
+      <c r="E292" s="39"/>
+      <c r="F292" s="39"/>
+      <c r="G292" s="39"/>
+      <c r="H292" s="39"/>
+      <c r="I292" s="39"/>
+      <c r="J292" s="39"/>
     </row>
     <row r="293" ht="37.5" customHeight="1" spans="2:10">
       <c r="B293" s="66">
@@ -12560,8 +12632,8 @@
       <c r="G293" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H293" s="32"/>
-      <c r="I293" s="37" t="s">
+      <c r="H293" s="35"/>
+      <c r="I293" s="36" t="s">
         <v>557</v>
       </c>
       <c r="J293" s="6" t="s">
@@ -12587,8 +12659,8 @@
       <c r="G294" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H294" s="32"/>
-      <c r="I294" s="37" t="s">
+      <c r="H294" s="35"/>
+      <c r="I294" s="36" t="s">
         <v>559</v>
       </c>
       <c r="J294" s="6" t="s">
@@ -12614,8 +12686,8 @@
       <c r="G295" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H295" s="32"/>
-      <c r="I295" s="37" t="s">
+      <c r="H295" s="35"/>
+      <c r="I295" s="36" t="s">
         <v>561</v>
       </c>
       <c r="J295" s="6" t="s">
@@ -12641,8 +12713,8 @@
       <c r="G296" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H296" s="32"/>
-      <c r="I296" s="37" t="s">
+      <c r="H296" s="35"/>
+      <c r="I296" s="36" t="s">
         <v>563</v>
       </c>
       <c r="J296" s="6" t="s">
@@ -12668,8 +12740,8 @@
       <c r="G297" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H297" s="32"/>
-      <c r="I297" s="37" t="s">
+      <c r="H297" s="35"/>
+      <c r="I297" s="36" t="s">
         <v>565</v>
       </c>
       <c r="J297" s="6" t="s">
@@ -12695,8 +12767,8 @@
       <c r="G298" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H298" s="32"/>
-      <c r="I298" s="37" t="s">
+      <c r="H298" s="35"/>
+      <c r="I298" s="36" t="s">
         <v>567</v>
       </c>
       <c r="J298" s="6" t="s">
@@ -12722,8 +12794,8 @@
       <c r="G299" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H299" s="32"/>
-      <c r="I299" s="37" t="s">
+      <c r="H299" s="35"/>
+      <c r="I299" s="36" t="s">
         <v>569</v>
       </c>
       <c r="J299" s="6" t="s">
@@ -12731,15 +12803,15 @@
       </c>
     </row>
     <row r="300" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B300" s="33"/>
-      <c r="C300" s="33"/>
-      <c r="D300" s="33"/>
-      <c r="E300" s="33"/>
-      <c r="F300" s="33"/>
-      <c r="G300" s="33"/>
-      <c r="H300" s="33"/>
-      <c r="I300" s="33"/>
-      <c r="J300" s="33"/>
+      <c r="B300" s="39"/>
+      <c r="C300" s="39"/>
+      <c r="D300" s="39"/>
+      <c r="E300" s="39"/>
+      <c r="F300" s="39"/>
+      <c r="G300" s="39"/>
+      <c r="H300" s="39"/>
+      <c r="I300" s="39"/>
+      <c r="J300" s="39"/>
     </row>
     <row r="301" ht="37.5" customHeight="1" spans="2:10">
       <c r="B301" s="66">
@@ -12760,8 +12832,8 @@
       <c r="G301" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H301" s="32"/>
-      <c r="I301" s="37" t="s">
+      <c r="H301" s="35"/>
+      <c r="I301" s="36" t="s">
         <v>571</v>
       </c>
       <c r="J301" s="6" t="s">
@@ -12787,8 +12859,8 @@
       <c r="G302" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H302" s="32"/>
-      <c r="I302" s="37" t="s">
+      <c r="H302" s="35"/>
+      <c r="I302" s="36" t="s">
         <v>573</v>
       </c>
       <c r="J302" s="6" t="s">
@@ -12814,8 +12886,8 @@
       <c r="G303" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H303" s="32"/>
-      <c r="I303" s="37" t="s">
+      <c r="H303" s="35"/>
+      <c r="I303" s="36" t="s">
         <v>575</v>
       </c>
       <c r="J303" s="6" t="s">
@@ -12841,8 +12913,8 @@
       <c r="G304" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H304" s="32"/>
-      <c r="I304" s="37" t="s">
+      <c r="H304" s="35"/>
+      <c r="I304" s="36" t="s">
         <v>577</v>
       </c>
       <c r="J304" s="6" t="s">
@@ -12868,8 +12940,8 @@
       <c r="G305" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H305" s="32"/>
-      <c r="I305" s="37" t="s">
+      <c r="H305" s="35"/>
+      <c r="I305" s="36" t="s">
         <v>579</v>
       </c>
       <c r="J305" s="6" t="s">
@@ -12895,8 +12967,8 @@
       <c r="G306" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H306" s="32"/>
-      <c r="I306" s="37" t="s">
+      <c r="H306" s="35"/>
+      <c r="I306" s="36" t="s">
         <v>581</v>
       </c>
       <c r="J306" s="6" t="s">
@@ -12922,8 +12994,8 @@
       <c r="G307" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H307" s="32"/>
-      <c r="I307" s="37" t="s">
+      <c r="H307" s="35"/>
+      <c r="I307" s="36" t="s">
         <v>583</v>
       </c>
       <c r="J307" s="6" t="s">
@@ -12931,15 +13003,15 @@
       </c>
     </row>
     <row r="308" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B308" s="33"/>
-      <c r="C308" s="33"/>
-      <c r="D308" s="33"/>
-      <c r="E308" s="33"/>
-      <c r="F308" s="33"/>
-      <c r="G308" s="33"/>
-      <c r="H308" s="33"/>
-      <c r="I308" s="33"/>
-      <c r="J308" s="33"/>
+      <c r="B308" s="39"/>
+      <c r="C308" s="39"/>
+      <c r="D308" s="39"/>
+      <c r="E308" s="39"/>
+      <c r="F308" s="39"/>
+      <c r="G308" s="39"/>
+      <c r="H308" s="39"/>
+      <c r="I308" s="39"/>
+      <c r="J308" s="39"/>
     </row>
     <row r="309" ht="37.5" customHeight="1" spans="2:10">
       <c r="B309" s="66">
@@ -12960,8 +13032,8 @@
       <c r="G309" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H309" s="32"/>
-      <c r="I309" s="37" t="s">
+      <c r="H309" s="35"/>
+      <c r="I309" s="36" t="s">
         <v>585</v>
       </c>
       <c r="J309" s="6" t="s">
@@ -12987,8 +13059,8 @@
       <c r="G310" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H310" s="32"/>
-      <c r="I310" s="37" t="s">
+      <c r="H310" s="35"/>
+      <c r="I310" s="36" t="s">
         <v>587</v>
       </c>
       <c r="J310" s="6" t="s">
@@ -13014,8 +13086,8 @@
       <c r="G311" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H311" s="32"/>
-      <c r="I311" s="37" t="s">
+      <c r="H311" s="35"/>
+      <c r="I311" s="36" t="s">
         <v>589</v>
       </c>
       <c r="J311" s="6" t="s">
@@ -13041,8 +13113,8 @@
       <c r="G312" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H312" s="32"/>
-      <c r="I312" s="37" t="s">
+      <c r="H312" s="35"/>
+      <c r="I312" s="36" t="s">
         <v>591</v>
       </c>
       <c r="J312" s="6" t="s">
@@ -13068,8 +13140,8 @@
       <c r="G313" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H313" s="32"/>
-      <c r="I313" s="37" t="s">
+      <c r="H313" s="35"/>
+      <c r="I313" s="36" t="s">
         <v>593</v>
       </c>
       <c r="J313" s="6" t="s">
@@ -13095,8 +13167,8 @@
       <c r="G314" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H314" s="32"/>
-      <c r="I314" s="37" t="s">
+      <c r="H314" s="35"/>
+      <c r="I314" s="36" t="s">
         <v>595</v>
       </c>
       <c r="J314" s="6" t="s">
@@ -13122,8 +13194,8 @@
       <c r="G315" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H315" s="32"/>
-      <c r="I315" s="37" t="s">
+      <c r="H315" s="35"/>
+      <c r="I315" s="36" t="s">
         <v>597</v>
       </c>
       <c r="J315" s="6" t="s">
@@ -13131,15 +13203,15 @@
       </c>
     </row>
     <row r="316" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B316" s="33"/>
-      <c r="C316" s="33"/>
-      <c r="D316" s="33"/>
-      <c r="E316" s="33"/>
-      <c r="F316" s="33"/>
-      <c r="G316" s="33"/>
-      <c r="H316" s="33"/>
-      <c r="I316" s="33"/>
-      <c r="J316" s="33"/>
+      <c r="B316" s="39"/>
+      <c r="C316" s="39"/>
+      <c r="D316" s="39"/>
+      <c r="E316" s="39"/>
+      <c r="F316" s="39"/>
+      <c r="G316" s="39"/>
+      <c r="H316" s="39"/>
+      <c r="I316" s="39"/>
+      <c r="J316" s="39"/>
     </row>
     <row r="317" ht="37.5" customHeight="1" spans="2:10">
       <c r="B317" s="66">
@@ -13160,8 +13232,8 @@
       <c r="G317" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H317" s="32"/>
-      <c r="I317" s="37" t="s">
+      <c r="H317" s="35"/>
+      <c r="I317" s="36" t="s">
         <v>599</v>
       </c>
       <c r="J317" s="6" t="s">
@@ -13187,8 +13259,8 @@
       <c r="G318" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H318" s="32"/>
-      <c r="I318" s="37" t="s">
+      <c r="H318" s="35"/>
+      <c r="I318" s="36" t="s">
         <v>601</v>
       </c>
       <c r="J318" s="6" t="s">
@@ -13214,8 +13286,8 @@
       <c r="G319" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H319" s="32"/>
-      <c r="I319" s="37" t="s">
+      <c r="H319" s="35"/>
+      <c r="I319" s="36" t="s">
         <v>603</v>
       </c>
       <c r="J319" s="6" t="s">
@@ -13241,8 +13313,8 @@
       <c r="G320" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H320" s="32"/>
-      <c r="I320" s="37" t="s">
+      <c r="H320" s="35"/>
+      <c r="I320" s="36" t="s">
         <v>605</v>
       </c>
       <c r="J320" s="6" t="s">
@@ -13268,8 +13340,8 @@
       <c r="G321" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H321" s="32"/>
-      <c r="I321" s="37" t="s">
+      <c r="H321" s="35"/>
+      <c r="I321" s="36" t="s">
         <v>607</v>
       </c>
       <c r="J321" s="6" t="s">
@@ -13295,8 +13367,8 @@
       <c r="G322" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H322" s="32"/>
-      <c r="I322" s="37" t="s">
+      <c r="H322" s="35"/>
+      <c r="I322" s="36" t="s">
         <v>609</v>
       </c>
       <c r="J322" s="6" t="s">
@@ -13322,8 +13394,8 @@
       <c r="G323" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H323" s="32"/>
-      <c r="I323" s="37" t="s">
+      <c r="H323" s="35"/>
+      <c r="I323" s="36" t="s">
         <v>611</v>
       </c>
       <c r="J323" s="6" t="s">
@@ -13331,15 +13403,15 @@
       </c>
     </row>
     <row r="324" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B324" s="33"/>
-      <c r="C324" s="33"/>
-      <c r="D324" s="33"/>
-      <c r="E324" s="33"/>
-      <c r="F324" s="33"/>
-      <c r="G324" s="33"/>
-      <c r="H324" s="33"/>
-      <c r="I324" s="33"/>
-      <c r="J324" s="33"/>
+      <c r="B324" s="39"/>
+      <c r="C324" s="39"/>
+      <c r="D324" s="39"/>
+      <c r="E324" s="39"/>
+      <c r="F324" s="39"/>
+      <c r="G324" s="39"/>
+      <c r="H324" s="39"/>
+      <c r="I324" s="39"/>
+      <c r="J324" s="39"/>
     </row>
     <row r="325" ht="37.5" customHeight="1" spans="2:10">
       <c r="B325" s="66">
@@ -13360,8 +13432,8 @@
       <c r="G325" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H325" s="32"/>
-      <c r="I325" s="37" t="s">
+      <c r="H325" s="35"/>
+      <c r="I325" s="36" t="s">
         <v>613</v>
       </c>
       <c r="J325" s="6" t="s">
@@ -13387,8 +13459,8 @@
       <c r="G326" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H326" s="32"/>
-      <c r="I326" s="37" t="s">
+      <c r="H326" s="35"/>
+      <c r="I326" s="36" t="s">
         <v>615</v>
       </c>
       <c r="J326" s="6" t="s">
@@ -13414,8 +13486,8 @@
       <c r="G327" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H327" s="32"/>
-      <c r="I327" s="37" t="s">
+      <c r="H327" s="35"/>
+      <c r="I327" s="36" t="s">
         <v>617</v>
       </c>
       <c r="J327" s="6" t="s">
@@ -13441,8 +13513,8 @@
       <c r="G328" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H328" s="32"/>
-      <c r="I328" s="37" t="s">
+      <c r="H328" s="35"/>
+      <c r="I328" s="36" t="s">
         <v>619</v>
       </c>
       <c r="J328" s="6" t="s">
@@ -13468,8 +13540,8 @@
       <c r="G329" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H329" s="32"/>
-      <c r="I329" s="37" t="s">
+      <c r="H329" s="35"/>
+      <c r="I329" s="36" t="s">
         <v>621</v>
       </c>
       <c r="J329" s="6" t="s">
@@ -13495,8 +13567,8 @@
       <c r="G330" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H330" s="32"/>
-      <c r="I330" s="37" t="s">
+      <c r="H330" s="35"/>
+      <c r="I330" s="36" t="s">
         <v>623</v>
       </c>
       <c r="J330" s="6" t="s">
@@ -13522,8 +13594,8 @@
       <c r="G331" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="H331" s="32"/>
-      <c r="I331" s="37" t="s">
+      <c r="H331" s="35"/>
+      <c r="I331" s="36" t="s">
         <v>625</v>
       </c>
       <c r="J331" s="6" t="s">
@@ -13531,15 +13603,15 @@
       </c>
     </row>
     <row r="332" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B332" s="33"/>
-      <c r="C332" s="33"/>
-      <c r="D332" s="33"/>
-      <c r="E332" s="33"/>
-      <c r="F332" s="33"/>
-      <c r="G332" s="33"/>
-      <c r="H332" s="33"/>
-      <c r="I332" s="33"/>
-      <c r="J332" s="33"/>
+      <c r="B332" s="39"/>
+      <c r="C332" s="39"/>
+      <c r="D332" s="39"/>
+      <c r="E332" s="39"/>
+      <c r="F332" s="39"/>
+      <c r="G332" s="39"/>
+      <c r="H332" s="39"/>
+      <c r="I332" s="39"/>
+      <c r="J332" s="39"/>
     </row>
     <row r="333" ht="13.5" customHeight="1" spans="2:10">
       <c r="B333" s="71" t="s">
@@ -13584,8 +13656,8 @@
       <c r="G335" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H335" s="32"/>
-      <c r="I335" s="37" t="s">
+      <c r="H335" s="35"/>
+      <c r="I335" s="36" t="s">
         <v>628</v>
       </c>
       <c r="J335" s="6" t="s">
@@ -13611,8 +13683,8 @@
       <c r="G336" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H336" s="32"/>
-      <c r="I336" s="37" t="s">
+      <c r="H336" s="35"/>
+      <c r="I336" s="36" t="s">
         <v>631</v>
       </c>
       <c r="J336" s="6" t="s">
@@ -13638,8 +13710,8 @@
       <c r="G337" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H337" s="32"/>
-      <c r="I337" s="37" t="s">
+      <c r="H337" s="35"/>
+      <c r="I337" s="36" t="s">
         <v>633</v>
       </c>
       <c r="J337" s="6" t="s">
@@ -13665,8 +13737,8 @@
       <c r="G338" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H338" s="32"/>
-      <c r="I338" s="37" t="s">
+      <c r="H338" s="35"/>
+      <c r="I338" s="36" t="s">
         <v>635</v>
       </c>
       <c r="J338" s="6" t="s">
@@ -13692,8 +13764,8 @@
       <c r="G339" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H339" s="32"/>
-      <c r="I339" s="37" t="s">
+      <c r="H339" s="35"/>
+      <c r="I339" s="36" t="s">
         <v>637</v>
       </c>
       <c r="J339" s="6" t="s">
@@ -13719,8 +13791,8 @@
       <c r="G340" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H340" s="32"/>
-      <c r="I340" s="37" t="s">
+      <c r="H340" s="35"/>
+      <c r="I340" s="36" t="s">
         <v>639</v>
       </c>
       <c r="J340" s="6" t="s">
@@ -13746,8 +13818,8 @@
       <c r="G341" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H341" s="32"/>
-      <c r="I341" s="37" t="s">
+      <c r="H341" s="35"/>
+      <c r="I341" s="36" t="s">
         <v>641</v>
       </c>
       <c r="J341" s="6" t="s">
@@ -13755,15 +13827,15 @@
       </c>
     </row>
     <row r="342" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B342" s="33"/>
-      <c r="C342" s="33"/>
-      <c r="D342" s="33"/>
-      <c r="E342" s="33"/>
-      <c r="F342" s="33"/>
-      <c r="G342" s="33"/>
-      <c r="H342" s="33"/>
-      <c r="I342" s="33"/>
-      <c r="J342" s="33"/>
+      <c r="B342" s="39"/>
+      <c r="C342" s="39"/>
+      <c r="D342" s="39"/>
+      <c r="E342" s="39"/>
+      <c r="F342" s="39"/>
+      <c r="G342" s="39"/>
+      <c r="H342" s="39"/>
+      <c r="I342" s="39"/>
+      <c r="J342" s="39"/>
     </row>
     <row r="343" ht="37.5" customHeight="1" spans="2:10">
       <c r="B343" s="72">
@@ -13784,8 +13856,8 @@
       <c r="G343" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H343" s="32"/>
-      <c r="I343" s="37" t="s">
+      <c r="H343" s="35"/>
+      <c r="I343" s="36" t="s">
         <v>643</v>
       </c>
       <c r="J343" s="6" t="s">
@@ -13811,8 +13883,8 @@
       <c r="G344" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H344" s="32"/>
-      <c r="I344" s="37" t="s">
+      <c r="H344" s="35"/>
+      <c r="I344" s="36" t="s">
         <v>645</v>
       </c>
       <c r="J344" s="6" t="s">
@@ -13838,8 +13910,8 @@
       <c r="G345" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H345" s="32"/>
-      <c r="I345" s="37" t="s">
+      <c r="H345" s="35"/>
+      <c r="I345" s="36" t="s">
         <v>647</v>
       </c>
       <c r="J345" s="6" t="s">
@@ -13865,8 +13937,8 @@
       <c r="G346" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H346" s="32"/>
-      <c r="I346" s="37" t="s">
+      <c r="H346" s="35"/>
+      <c r="I346" s="36" t="s">
         <v>649</v>
       </c>
       <c r="J346" s="6" t="s">
@@ -13892,8 +13964,8 @@
       <c r="G347" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H347" s="32"/>
-      <c r="I347" s="37" t="s">
+      <c r="H347" s="35"/>
+      <c r="I347" s="36" t="s">
         <v>651</v>
       </c>
       <c r="J347" s="6" t="s">
@@ -13919,8 +13991,8 @@
       <c r="G348" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H348" s="32"/>
-      <c r="I348" s="37" t="s">
+      <c r="H348" s="35"/>
+      <c r="I348" s="36" t="s">
         <v>653</v>
       </c>
       <c r="J348" s="6" t="s">
@@ -13946,8 +14018,8 @@
       <c r="G349" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H349" s="32"/>
-      <c r="I349" s="37" t="s">
+      <c r="H349" s="35"/>
+      <c r="I349" s="36" t="s">
         <v>655</v>
       </c>
       <c r="J349" s="6" t="s">
@@ -13955,15 +14027,15 @@
       </c>
     </row>
     <row r="350" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B350" s="33"/>
-      <c r="C350" s="33"/>
-      <c r="D350" s="33"/>
-      <c r="E350" s="33"/>
-      <c r="F350" s="33"/>
-      <c r="G350" s="33"/>
-      <c r="H350" s="33"/>
-      <c r="I350" s="33"/>
-      <c r="J350" s="33"/>
+      <c r="B350" s="39"/>
+      <c r="C350" s="39"/>
+      <c r="D350" s="39"/>
+      <c r="E350" s="39"/>
+      <c r="F350" s="39"/>
+      <c r="G350" s="39"/>
+      <c r="H350" s="39"/>
+      <c r="I350" s="39"/>
+      <c r="J350" s="39"/>
     </row>
     <row r="351" ht="37.5" customHeight="1" spans="2:10">
       <c r="B351" s="72">
@@ -13984,8 +14056,8 @@
       <c r="G351" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H351" s="32"/>
-      <c r="I351" s="37" t="s">
+      <c r="H351" s="35"/>
+      <c r="I351" s="36" t="s">
         <v>657</v>
       </c>
       <c r="J351" s="6" t="s">
@@ -14011,8 +14083,8 @@
       <c r="G352" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H352" s="32"/>
-      <c r="I352" s="37" t="s">
+      <c r="H352" s="35"/>
+      <c r="I352" s="36" t="s">
         <v>659</v>
       </c>
       <c r="J352" s="6" t="s">
@@ -14038,8 +14110,8 @@
       <c r="G353" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H353" s="32"/>
-      <c r="I353" s="37" t="s">
+      <c r="H353" s="35"/>
+      <c r="I353" s="36" t="s">
         <v>661</v>
       </c>
       <c r="J353" s="6" t="s">
@@ -14065,8 +14137,8 @@
       <c r="G354" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H354" s="32"/>
-      <c r="I354" s="37" t="s">
+      <c r="H354" s="35"/>
+      <c r="I354" s="36" t="s">
         <v>663</v>
       </c>
       <c r="J354" s="6" t="s">
@@ -14092,8 +14164,8 @@
       <c r="G355" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H355" s="32"/>
-      <c r="I355" s="37" t="s">
+      <c r="H355" s="35"/>
+      <c r="I355" s="36" t="s">
         <v>665</v>
       </c>
       <c r="J355" s="6" t="s">
@@ -14119,8 +14191,8 @@
       <c r="G356" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H356" s="32"/>
-      <c r="I356" s="37" t="s">
+      <c r="H356" s="35"/>
+      <c r="I356" s="36" t="s">
         <v>667</v>
       </c>
       <c r="J356" s="6" t="s">
@@ -14146,8 +14218,8 @@
       <c r="G357" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H357" s="32"/>
-      <c r="I357" s="37" t="s">
+      <c r="H357" s="35"/>
+      <c r="I357" s="36" t="s">
         <v>669</v>
       </c>
       <c r="J357" s="6" t="s">
@@ -14155,15 +14227,15 @@
       </c>
     </row>
     <row r="358" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B358" s="33"/>
-      <c r="C358" s="33"/>
-      <c r="D358" s="33"/>
-      <c r="E358" s="33"/>
-      <c r="F358" s="33"/>
-      <c r="G358" s="33"/>
-      <c r="H358" s="33"/>
-      <c r="I358" s="33"/>
-      <c r="J358" s="33"/>
+      <c r="B358" s="39"/>
+      <c r="C358" s="39"/>
+      <c r="D358" s="39"/>
+      <c r="E358" s="39"/>
+      <c r="F358" s="39"/>
+      <c r="G358" s="39"/>
+      <c r="H358" s="39"/>
+      <c r="I358" s="39"/>
+      <c r="J358" s="39"/>
     </row>
     <row r="359" ht="37.5" customHeight="1" spans="2:10">
       <c r="B359" s="72">
@@ -14184,8 +14256,8 @@
       <c r="G359" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H359" s="32"/>
-      <c r="I359" s="37" t="s">
+      <c r="H359" s="35"/>
+      <c r="I359" s="36" t="s">
         <v>671</v>
       </c>
       <c r="J359" s="6" t="s">
@@ -14211,8 +14283,8 @@
       <c r="G360" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H360" s="32"/>
-      <c r="I360" s="37" t="s">
+      <c r="H360" s="35"/>
+      <c r="I360" s="36" t="s">
         <v>673</v>
       </c>
       <c r="J360" s="6" t="s">
@@ -14238,8 +14310,8 @@
       <c r="G361" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H361" s="32"/>
-      <c r="I361" s="37" t="s">
+      <c r="H361" s="35"/>
+      <c r="I361" s="36" t="s">
         <v>675</v>
       </c>
       <c r="J361" s="6" t="s">
@@ -14265,8 +14337,8 @@
       <c r="G362" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H362" s="32"/>
-      <c r="I362" s="37" t="s">
+      <c r="H362" s="35"/>
+      <c r="I362" s="36" t="s">
         <v>677</v>
       </c>
       <c r="J362" s="6" t="s">
@@ -14292,8 +14364,8 @@
       <c r="G363" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H363" s="32"/>
-      <c r="I363" s="37" t="s">
+      <c r="H363" s="35"/>
+      <c r="I363" s="36" t="s">
         <v>679</v>
       </c>
       <c r="J363" s="6" t="s">
@@ -14319,8 +14391,8 @@
       <c r="G364" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H364" s="32"/>
-      <c r="I364" s="37" t="s">
+      <c r="H364" s="35"/>
+      <c r="I364" s="36" t="s">
         <v>681</v>
       </c>
       <c r="J364" s="6" t="s">
@@ -14346,8 +14418,8 @@
       <c r="G365" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="H365" s="32"/>
-      <c r="I365" s="37" t="s">
+      <c r="H365" s="35"/>
+      <c r="I365" s="36" t="s">
         <v>683</v>
       </c>
       <c r="J365" s="6" t="s">
@@ -14355,15 +14427,15 @@
       </c>
     </row>
     <row r="366" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B366" s="33"/>
-      <c r="C366" s="33"/>
-      <c r="D366" s="33"/>
-      <c r="E366" s="33"/>
-      <c r="F366" s="33"/>
-      <c r="G366" s="33"/>
-      <c r="H366" s="33"/>
-      <c r="I366" s="33"/>
-      <c r="J366" s="33"/>
+      <c r="B366" s="39"/>
+      <c r="C366" s="39"/>
+      <c r="D366" s="39"/>
+      <c r="E366" s="39"/>
+      <c r="F366" s="39"/>
+      <c r="G366" s="39"/>
+      <c r="H366" s="39"/>
+      <c r="I366" s="39"/>
+      <c r="J366" s="39"/>
     </row>
     <row r="367" ht="13.5" customHeight="1" spans="2:10">
       <c r="B367" s="77" t="s">
@@ -14408,8 +14480,8 @@
       <c r="G369" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H369" s="32"/>
-      <c r="I369" s="37" t="s">
+      <c r="H369" s="35"/>
+      <c r="I369" s="36" t="s">
         <v>686</v>
       </c>
       <c r="J369" s="6" t="s">
@@ -14435,8 +14507,8 @@
       <c r="G370" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H370" s="32"/>
-      <c r="I370" s="37" t="s">
+      <c r="H370" s="35"/>
+      <c r="I370" s="36" t="s">
         <v>689</v>
       </c>
       <c r="J370" s="6" t="s">
@@ -14462,8 +14534,8 @@
       <c r="G371" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H371" s="32"/>
-      <c r="I371" s="37" t="s">
+      <c r="H371" s="35"/>
+      <c r="I371" s="36" t="s">
         <v>691</v>
       </c>
       <c r="J371" s="6" t="s">
@@ -14489,8 +14561,8 @@
       <c r="G372" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H372" s="32"/>
-      <c r="I372" s="37" t="s">
+      <c r="H372" s="35"/>
+      <c r="I372" s="36" t="s">
         <v>693</v>
       </c>
       <c r="J372" s="6" t="s">
@@ -14516,8 +14588,8 @@
       <c r="G373" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H373" s="32"/>
-      <c r="I373" s="37" t="s">
+      <c r="H373" s="35"/>
+      <c r="I373" s="36" t="s">
         <v>695</v>
       </c>
       <c r="J373" s="6" t="s">
@@ -14543,8 +14615,8 @@
       <c r="G374" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H374" s="32"/>
-      <c r="I374" s="37" t="s">
+      <c r="H374" s="35"/>
+      <c r="I374" s="36" t="s">
         <v>697</v>
       </c>
       <c r="J374" s="6" t="s">
@@ -14570,8 +14642,8 @@
       <c r="G375" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H375" s="32"/>
-      <c r="I375" s="37" t="s">
+      <c r="H375" s="35"/>
+      <c r="I375" s="36" t="s">
         <v>699</v>
       </c>
       <c r="J375" s="6" t="s">
@@ -14579,15 +14651,15 @@
       </c>
     </row>
     <row r="376" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B376" s="33"/>
-      <c r="C376" s="33"/>
-      <c r="D376" s="33"/>
-      <c r="E376" s="33"/>
-      <c r="F376" s="33"/>
-      <c r="G376" s="33"/>
-      <c r="H376" s="33"/>
-      <c r="I376" s="33"/>
-      <c r="J376" s="33"/>
+      <c r="B376" s="39"/>
+      <c r="C376" s="39"/>
+      <c r="D376" s="39"/>
+      <c r="E376" s="39"/>
+      <c r="F376" s="39"/>
+      <c r="G376" s="39"/>
+      <c r="H376" s="39"/>
+      <c r="I376" s="39"/>
+      <c r="J376" s="39"/>
     </row>
     <row r="377" ht="37.5" customHeight="1" spans="2:10">
       <c r="B377" s="78">
@@ -14608,8 +14680,8 @@
       <c r="G377" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H377" s="32"/>
-      <c r="I377" s="37" t="s">
+      <c r="H377" s="35"/>
+      <c r="I377" s="36" t="s">
         <v>701</v>
       </c>
       <c r="J377" s="6" t="s">
@@ -14635,8 +14707,8 @@
       <c r="G378" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H378" s="32"/>
-      <c r="I378" s="37" t="s">
+      <c r="H378" s="35"/>
+      <c r="I378" s="36" t="s">
         <v>703</v>
       </c>
       <c r="J378" s="6" t="s">
@@ -14662,8 +14734,8 @@
       <c r="G379" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H379" s="32"/>
-      <c r="I379" s="37" t="s">
+      <c r="H379" s="35"/>
+      <c r="I379" s="36" t="s">
         <v>705</v>
       </c>
       <c r="J379" s="6" t="s">
@@ -14689,8 +14761,8 @@
       <c r="G380" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H380" s="32"/>
-      <c r="I380" s="37" t="s">
+      <c r="H380" s="35"/>
+      <c r="I380" s="36" t="s">
         <v>707</v>
       </c>
       <c r="J380" s="6" t="s">
@@ -14716,8 +14788,8 @@
       <c r="G381" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H381" s="32"/>
-      <c r="I381" s="37" t="s">
+      <c r="H381" s="35"/>
+      <c r="I381" s="36" t="s">
         <v>709</v>
       </c>
       <c r="J381" s="6" t="s">
@@ -14743,8 +14815,8 @@
       <c r="G382" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H382" s="32"/>
-      <c r="I382" s="37" t="s">
+      <c r="H382" s="35"/>
+      <c r="I382" s="36" t="s">
         <v>711</v>
       </c>
       <c r="J382" s="6" t="s">
@@ -14770,8 +14842,8 @@
       <c r="G383" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H383" s="32"/>
-      <c r="I383" s="37" t="s">
+      <c r="H383" s="35"/>
+      <c r="I383" s="36" t="s">
         <v>713</v>
       </c>
       <c r="J383" s="6" t="s">
@@ -14779,15 +14851,15 @@
       </c>
     </row>
     <row r="384" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B384" s="33"/>
-      <c r="C384" s="33"/>
-      <c r="D384" s="33"/>
-      <c r="E384" s="33"/>
-      <c r="F384" s="33"/>
-      <c r="G384" s="33"/>
-      <c r="H384" s="33"/>
-      <c r="I384" s="33"/>
-      <c r="J384" s="33"/>
+      <c r="B384" s="39"/>
+      <c r="C384" s="39"/>
+      <c r="D384" s="39"/>
+      <c r="E384" s="39"/>
+      <c r="F384" s="39"/>
+      <c r="G384" s="39"/>
+      <c r="H384" s="39"/>
+      <c r="I384" s="39"/>
+      <c r="J384" s="39"/>
     </row>
     <row r="385" ht="37.5" customHeight="1" spans="2:10">
       <c r="B385" s="78">
@@ -14808,8 +14880,8 @@
       <c r="G385" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H385" s="32"/>
-      <c r="I385" s="37" t="s">
+      <c r="H385" s="35"/>
+      <c r="I385" s="36" t="s">
         <v>715</v>
       </c>
       <c r="J385" s="6" t="s">
@@ -14835,8 +14907,8 @@
       <c r="G386" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H386" s="32"/>
-      <c r="I386" s="37" t="s">
+      <c r="H386" s="35"/>
+      <c r="I386" s="36" t="s">
         <v>717</v>
       </c>
       <c r="J386" s="6" t="s">
@@ -14862,8 +14934,8 @@
       <c r="G387" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H387" s="32"/>
-      <c r="I387" s="37" t="s">
+      <c r="H387" s="35"/>
+      <c r="I387" s="36" t="s">
         <v>719</v>
       </c>
       <c r="J387" s="6" t="s">
@@ -14889,8 +14961,8 @@
       <c r="G388" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H388" s="32"/>
-      <c r="I388" s="37" t="s">
+      <c r="H388" s="35"/>
+      <c r="I388" s="36" t="s">
         <v>721</v>
       </c>
       <c r="J388" s="6" t="s">
@@ -14916,8 +14988,8 @@
       <c r="G389" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H389" s="32"/>
-      <c r="I389" s="37" t="s">
+      <c r="H389" s="35"/>
+      <c r="I389" s="36" t="s">
         <v>723</v>
       </c>
       <c r="J389" s="6" t="s">
@@ -14943,8 +15015,8 @@
       <c r="G390" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H390" s="32"/>
-      <c r="I390" s="37" t="s">
+      <c r="H390" s="35"/>
+      <c r="I390" s="36" t="s">
         <v>725</v>
       </c>
       <c r="J390" s="6" t="s">
@@ -14970,8 +15042,8 @@
       <c r="G391" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H391" s="32"/>
-      <c r="I391" s="37" t="s">
+      <c r="H391" s="35"/>
+      <c r="I391" s="36" t="s">
         <v>727</v>
       </c>
       <c r="J391" s="6" t="s">
@@ -14979,15 +15051,15 @@
       </c>
     </row>
     <row r="392" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B392" s="33"/>
-      <c r="C392" s="33"/>
-      <c r="D392" s="33"/>
-      <c r="E392" s="33"/>
-      <c r="F392" s="33"/>
-      <c r="G392" s="33"/>
-      <c r="H392" s="33"/>
-      <c r="I392" s="33"/>
-      <c r="J392" s="33"/>
+      <c r="B392" s="39"/>
+      <c r="C392" s="39"/>
+      <c r="D392" s="39"/>
+      <c r="E392" s="39"/>
+      <c r="F392" s="39"/>
+      <c r="G392" s="39"/>
+      <c r="H392" s="39"/>
+      <c r="I392" s="39"/>
+      <c r="J392" s="39"/>
     </row>
     <row r="393" ht="37.5" customHeight="1" spans="2:10">
       <c r="B393" s="78">
@@ -15008,8 +15080,8 @@
       <c r="G393" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H393" s="32"/>
-      <c r="I393" s="37" t="s">
+      <c r="H393" s="35"/>
+      <c r="I393" s="36" t="s">
         <v>729</v>
       </c>
       <c r="J393" s="6" t="s">
@@ -15035,8 +15107,8 @@
       <c r="G394" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H394" s="32"/>
-      <c r="I394" s="37" t="s">
+      <c r="H394" s="35"/>
+      <c r="I394" s="36" t="s">
         <v>731</v>
       </c>
       <c r="J394" s="6" t="s">
@@ -15062,8 +15134,8 @@
       <c r="G395" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H395" s="32"/>
-      <c r="I395" s="37" t="s">
+      <c r="H395" s="35"/>
+      <c r="I395" s="36" t="s">
         <v>733</v>
       </c>
       <c r="J395" s="6" t="s">
@@ -15089,8 +15161,8 @@
       <c r="G396" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H396" s="32"/>
-      <c r="I396" s="37" t="s">
+      <c r="H396" s="35"/>
+      <c r="I396" s="36" t="s">
         <v>735</v>
       </c>
       <c r="J396" s="6" t="s">
@@ -15116,8 +15188,8 @@
       <c r="G397" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H397" s="32"/>
-      <c r="I397" s="37" t="s">
+      <c r="H397" s="35"/>
+      <c r="I397" s="36" t="s">
         <v>737</v>
       </c>
       <c r="J397" s="6" t="s">
@@ -15143,8 +15215,8 @@
       <c r="G398" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H398" s="32"/>
-      <c r="I398" s="37" t="s">
+      <c r="H398" s="35"/>
+      <c r="I398" s="36" t="s">
         <v>739</v>
       </c>
       <c r="J398" s="6" t="s">
@@ -15170,8 +15242,8 @@
       <c r="G399" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H399" s="32"/>
-      <c r="I399" s="37" t="s">
+      <c r="H399" s="35"/>
+      <c r="I399" s="36" t="s">
         <v>741</v>
       </c>
       <c r="J399" s="6" t="s">
@@ -15179,15 +15251,15 @@
       </c>
     </row>
     <row r="400" ht="7.5" customHeight="1" spans="2:10">
-      <c r="B400" s="33"/>
-      <c r="C400" s="33"/>
-      <c r="D400" s="33"/>
-      <c r="E400" s="33"/>
-      <c r="F400" s="33"/>
-      <c r="G400" s="33"/>
-      <c r="H400" s="33"/>
-      <c r="I400" s="33"/>
-      <c r="J400" s="33"/>
+      <c r="B400" s="39"/>
+      <c r="C400" s="39"/>
+      <c r="D400" s="39"/>
+      <c r="E400" s="39"/>
+      <c r="F400" s="39"/>
+      <c r="G400" s="39"/>
+      <c r="H400" s="39"/>
+      <c r="I400" s="39"/>
+      <c r="J400" s="39"/>
     </row>
     <row r="401" ht="13.5" customHeight="1" spans="2:10">
       <c r="B401" s="83" t="s">
@@ -15263,7 +15335,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="2:7">
+    <row r="2" ht="24" customHeight="1" spans="2:8">
       <c r="B2" s="2" t="s">
         <v>744</v>
       </c>
@@ -15283,7 +15355,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="2:7">
+    <row r="3" ht="31.5" customHeight="1" spans="2:8">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -15303,7 +15375,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="2:7">
+    <row r="4" ht="31.5" customHeight="1" spans="2:8">
       <c r="B4" s="7">
         <v>2</v>
       </c>
@@ -15323,7 +15395,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="5" ht="31.5" customHeight="1" spans="2:7">
+    <row r="5" ht="31.5" customHeight="1" spans="2:8">
       <c r="B5" s="10">
         <v>3</v>
       </c>
@@ -15343,7 +15415,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="6" ht="31.5" customHeight="1" spans="2:7">
+    <row r="6" ht="31.5" customHeight="1" spans="2:8">
       <c r="B6" s="13">
         <v>4</v>
       </c>
@@ -15363,7 +15435,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="7" ht="31.5" customHeight="1" spans="2:7">
+    <row r="7" ht="31.5" customHeight="1" spans="2:8">
       <c r="B7" s="15">
         <v>5</v>
       </c>
@@ -15383,7 +15455,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="8" ht="31.5" customHeight="1" spans="2:7">
+    <row r="8" ht="31.5" customHeight="1" spans="2:8">
       <c r="B8" s="18">
         <v>6</v>
       </c>
@@ -15403,7 +15475,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="9" ht="31.5" customHeight="1" spans="2:7">
+    <row r="9" ht="31.5" customHeight="1" spans="2:8">
       <c r="B9" s="20">
         <v>7</v>
       </c>
@@ -15423,7 +15495,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="10" ht="31.5" customHeight="1" spans="2:7">
+    <row r="10" ht="31.5" customHeight="1" spans="2:8">
       <c r="B10" s="23">
         <v>8</v>
       </c>

--- a/AI_ML_Daily_Tracker.xlsx
+++ b/AI_ML_Daily_Tracker.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="774">
   <si>
     <t>🤖  AI / ML ENGINEER – 12-MONTH STREAK TRACKER</t>
   </si>
@@ -4928,27 +4928,27 @@
     <row r="6" ht="49.5" customHeight="1" spans="2:12">
       <c r="B6" s="89">
         <f>'📅 Tracker'!P2</f>
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C6" s="89"/>
       <c r="D6" s="90">
         <f>'📅 Tracker'!P3</f>
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="E6" s="90"/>
       <c r="F6" s="91">
         <f>'📅 Tracker'!P4</f>
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G6" s="91"/>
       <c r="H6" s="92">
         <f>'📅 Tracker'!P5</f>
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I6" s="92"/>
       <c r="J6" s="93">
         <f>'📅 Tracker'!P6</f>
-        <v>14.8809523809524</v>
+        <v>18.1547619047619</v>
       </c>
       <c r="K6" s="93"/>
     </row>
@@ -5005,11 +5005,11 @@
       </c>
       <c r="H10" s="100">
         <f>COUNTIFS('📅 Tracker'!G:G,"Phase 1",'📅 Tracker'!H:H,"✓")</f>
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I10" s="101">
         <f>IFERROR(H10/56,0)</f>
-        <v>0.875</v>
+        <v>0.982142857142857</v>
       </c>
       <c r="J10" s="101"/>
       <c r="K10" s="101"/>
@@ -5031,11 +5031,11 @@
       </c>
       <c r="H11" s="105">
         <f>COUNTIFS('📅 Tracker'!G:G,"Phase 2",'📅 Tracker'!H:H,"✓")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I11" s="106">
         <f>IFERROR(H11/28,0)</f>
-        <v>0.0357142857142857</v>
+        <v>0.214285714285714</v>
       </c>
       <c r="J11" s="106"/>
       <c r="K11" s="106"/>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="P2" s="29">
         <f>COUNTIF(H3:H402,"✓")</f>
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1" spans="2:19">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="P3" s="29">
         <f>336-P2</f>
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="R3" s="37">
         <v>46074</v>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="P4" s="29">
         <f>IFERROR(MATCH(FALSE(),EXACT(H3:H338,"✓"),0)-1,COUNTIF(H3:H338,"✓"))</f>
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="R4" s="37">
         <v>46410</v>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="P5" s="29">
         <f>P2</f>
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" ht="37.5" customHeight="1" spans="2:19">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="P6" s="38">
         <f>IFERROR(P2/336*100,0)</f>
-        <v>14.8809523809524</v>
+        <v>18.1547619047619</v>
       </c>
     </row>
     <row r="7" ht="37.5" customHeight="1" spans="2:19">
@@ -6569,7 +6569,9 @@
       <c r="G46" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H46" s="35"/>
+      <c r="H46" s="35" t="s">
+        <v>49</v>
+      </c>
       <c r="I46" s="36" t="s">
         <v>133</v>
       </c>
@@ -6596,7 +6598,9 @@
       <c r="G47" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H47" s="35"/>
+      <c r="H47" s="35" t="s">
+        <v>49</v>
+      </c>
       <c r="I47" s="36" t="s">
         <v>135</v>
       </c>
@@ -6650,7 +6654,9 @@
       <c r="G49" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H49" s="35"/>
+      <c r="H49" s="35" t="s">
+        <v>49</v>
+      </c>
       <c r="I49" s="36" t="s">
         <v>139</v>
       </c>
@@ -6833,7 +6839,9 @@
       <c r="G56" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H56" s="35"/>
+      <c r="H56" s="35" t="s">
+        <v>49</v>
+      </c>
       <c r="I56" s="36" t="s">
         <v>151</v>
       </c>
@@ -6860,7 +6868,9 @@
       <c r="G57" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H57" s="35"/>
+      <c r="H57" s="35" t="s">
+        <v>49</v>
+      </c>
       <c r="I57" s="36" t="s">
         <v>153</v>
       </c>
@@ -7072,7 +7082,9 @@
       <c r="G65" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H65" s="35"/>
+      <c r="H65" s="35" t="s">
+        <v>49</v>
+      </c>
       <c r="I65" s="36" t="s">
         <v>167</v>
       </c>
@@ -7163,7 +7175,9 @@
       <c r="G70" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H70" s="35"/>
+      <c r="H70" s="35" t="s">
+        <v>49</v>
+      </c>
       <c r="I70" s="36" t="s">
         <v>173</v>
       </c>
@@ -7190,7 +7204,9 @@
       <c r="G71" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H71" s="35"/>
+      <c r="H71" s="35" t="s">
+        <v>49</v>
+      </c>
       <c r="I71" s="36" t="s">
         <v>175</v>
       </c>
@@ -7217,7 +7233,9 @@
       <c r="G72" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H72" s="35"/>
+      <c r="H72" s="35" t="s">
+        <v>49</v>
+      </c>
       <c r="I72" s="36" t="s">
         <v>177</v>
       </c>
@@ -7244,7 +7262,9 @@
       <c r="G73" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H73" s="35"/>
+      <c r="H73" s="35" t="s">
+        <v>49</v>
+      </c>
       <c r="I73" s="36" t="s">
         <v>179</v>
       </c>
@@ -7271,7 +7291,9 @@
       <c r="G74" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H74" s="35"/>
+      <c r="H74" s="35" t="s">
+        <v>49</v>
+      </c>
       <c r="I74" s="36" t="s">
         <v>181</v>
       </c>
